--- a/mimmolo_supplier_sourcing_sheet.xlsx
+++ b/mimmolo_supplier_sourcing_sheet.xlsx
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K185"/>
+  <dimension ref="A1:K107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -686,22 +686,22 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Owala 2-in-1 Bottle Brush</t>
+          <t>Starry Crochet Baby Suit</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>Accessory</t>
+          <t>Baby suit</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Sea Star / S (1–6 Months), Sea Star / M (6–12 Months), Sea Star / L (1–3 Years), Buttery Yellow / S (1–6 Months), Buttery Yellow / M (6–12 Months)</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>While at first it may seem like an ordinary brush, our Bottle Brush is a 2-in-1 cleaner. (Cue the oooohs and ahhhhs.) The brush itself has hundreds of germ-fighting bristles and it fits perfectly inside Owala bottles—making scrubbing easier than ever. Plus, the brush head is removable and dishwasher safe. But here’s where things get exciting: there</t>
+          <t>The crochet-knit star suit that turns everyday moments into the photos you'll keep forever. Soft against delicate skin, roomy enough to fit over a onesie, and adorable from every angle. Soft crochet knit — cosy texture, no scratchy seams Roomy star silhouette — slips on easily, fits over a onesie Three sizes — S (1–6 months), M (6–12 months), L (1–</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr"/>
@@ -721,22 +721,22 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Owala Bottle Boot</t>
+          <t>Snoopy Glass Cup</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Accessory</t>
+          <t>Glass cup</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>Light Pink / 16oz, Light Pink / 24oz, Light Pink / 32oz, Light Pink / 30oz / 40oz, Yellow / 16oz</t>
+          <t>Default Title</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>Dents and scratches? A thing of the past. No more worrying about dropping your bottle or placing it down too hard. This silicone cover acts like a phone case for your Owala Bottle—protecting it from damage and keeping it looking good as new. With an assortment of colors to choose from, the Bottle Boot also adds extra personality and individuality t</t>
+          <t>Snoopy, but make him a cup: a clear glass shaped like the world's favorite beagle, topped with a little orange beanie lid, a green scarf and a straw. The desk-drink upgrade that gets a "where did you get that" every single time.</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr"/>
@@ -756,22 +756,22 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Starry Crochet Baby Suit</t>
+          <t>Harry Styles Jellycat Bunny</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Baby suit</t>
+          <t>Plush</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Sea Star / S (1–6 Months), Sea Star / M (6–12 Months), Sea Star / L (1–3 Years), Buttery Yellow / S (1–6 Months), Buttery Yellow / M (6–12 Months)</t>
+          <t>Default Title</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>The crochet-knit star suit that turns everyday moments into the photos you'll keep forever. Soft against delicate skin, roomy enough to fit over a onesie, and adorable from every angle. Soft crochet knit — cosy texture, no scratchy seams Roomy star silhouette — slips on easily, fits over a onesie Three sizes — S (1–6 months), M (6–12 months), L (1–</t>
+          <t>A grey floppy-eared bunny with "Harry Styles" stitched on one ear and "Kiss me… all the time" and "Disco Occasion" on its paws. Soft, huggable, and very much the shelf piece for the fan in your life.</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr"/>
@@ -791,22 +791,22 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Owala The All-Day Crossbody</t>
+          <t>Weighted Cow Plush</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Bag</t>
+          <t>Plush</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Night Mode, Sahara, Sea Glass, Rest Azured, Out West</t>
+          <t>Default Title</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>Think of me as your bottle's hot plus-one. I'm here for your half-day hike. Your full-day music festival. Your theme park marathon. I've got space for your phone, wallet, keys, snacks, and a dedicated spot for your Owala bottle. Wear me crossbody, around your waist, front or back. I keep everything in place so you can keep going.</t>
+          <t>A fluffy highland cow with a gentle weight inside — the plush that works like a mini weighted blanket. Rest it on your lap, your chest or your belly for a calm, grounding hug at the end of the day. Gentle, evenly distributed weight for a calming feel Ultra-soft long-pile fur with tiny horns and a fringe Great for wind-down time, study breaks and tr</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr"/>
@@ -826,22 +826,22 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Owala The Cloud</t>
+          <t>HydroJug x Anthropologie 40 oz. Traveler</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Bag</t>
+          <t>Tumbler</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Rosewood, Al Fresco, Night Mode, Beige Babe</t>
+          <t>Default Title</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>I’m not here to blend in. I’m big, bold, and (you guessed it) beautiful. Inflate me when you need to keep things cool, collapse me when you’re ready to pack. I’ve got room for everything—drinks, snacks, even a five-course meal. Take me to the beach, your park hang, that rooftop party. I guarantee people will ask about me. Go ahead, make it a thing.</t>
+          <t>Cream with rows of green ribbon bows, a deep-green handle and lid. The coquette 40 oz traveler — pretty on the desk, practical in the car cup holder.</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr"/>
@@ -861,22 +861,22 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Owala The Daily Crossbody</t>
+          <t>PINK x HydroJug 40oz Tumbler</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Bag</t>
+          <t>Tumbler</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Oat Latte, Golden Hour, Coral Reef, Al Fresco, Night Mode</t>
+          <t>Default Title</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">I’m not high maintenance. I’m highly efficient. I keep just what you need right where you need it. I’m here for your city stroll. Your power pump class. Your quick weekend hike. I’ve got space for your phone, wallet, keys, and a few small extras plus a built-in way to clip on your water bottle and keep moving. Wear me crossbody, around your waist, </t>
+          <t>Bubblegum pink with a black leopard print, a matching pink handle and straw lid. The 40 oz traveler that goes from gym bag to car cup holder without spilling a drop.</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr"/>
@@ -896,22 +896,22 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Owala The Puffer</t>
+          <t>Polka Dot Hydrojug 40 Oz Tumbler</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Bag</t>
+          <t>Tumbler</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Rest Azured, Fern Fresh, After Hours, Hot Stuff, Sahara</t>
+          <t>Default Title</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>I keep things cool without trying too hard. I’m lightweight, packable, and ready for farmer market strolls, a round of golf, tailgating, or dinner with friends. Inflate me when you want to keep things cool, fold me flat when you don’t. I’ve got space for plenty of goodies plus an internal pocket to keep the small stuff organized. Easygoing, but sti</t>
+          <t>Cocoa brown with tiny cream polka dots, a matching handle and a straw lid. The 40 oz traveler that looks like a latte and holds a whole afternoon of ice water.</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr"/>
@@ -931,22 +931,22 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Owala The Puffer Mini</t>
+          <t>Sally x Jack Skellington 40oz Tumbler</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Bag</t>
+          <t>Tumbler</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Cloud Kiss, Fern Fresh, After Hours, Al Fresco, Beige Babe</t>
+          <t>Default Title</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">I’m small, but I’ve got main-character energy. I keep your snacks, drinks, and lunch perfectly cool because, let’s be honest, your lunch deserves better. Inflate me when you want to keep things cool, fold me flat when you don’t. I’m cute, I’m compact, and I go with everything. Desk lunch, beach snack, midday pick-me-up—I make it all (and you) look </t>
+          <t>Jack and Sally in a purple drip of stars, spiders and pumpkins, printed on a 40 oz tumbler that glows in the dark . Handle, straw lid, cup-holder base — and a moonlit glow once the porch light goes off.</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr"/>
@@ -966,22 +966,22 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Owala The Sun-Day Collapsible Tote</t>
+          <t>Tortoise Hydrojug 40 Oz Tumbler</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Bag</t>
+          <t>Tumbler</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Wavelength, Hot Tropic, Coastal Queen, Cowabunga, Sunkissed</t>
+          <t>Default Title</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>I’m water-friendly, built with soft-touch handles, and fully collapsible for easy travel and storage. I also come with an adjustable shoulder strap and an essentials pouch—because of course I do. So… where are we going?</t>
+          <t>Glossy tortoise shell in amber and black, with a black handle and lid. The 40 oz traveler that looks like your favorite sunglasses.</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr"/>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Owala The Sun-Day Tote</t>
+          <t>Winnie The Pooh 40 oz Tumbler</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Bag</t>
+          <t>Tumbler</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Checkin' In, Wavelength, Hot Tropic, Coastal Queen, Cowabunga</t>
+          <t>Standard Box, Gift Box 🎁</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>Think I’m just a beach bag? Think again. I’m your beach-day bestie. Your farmers market sidekick. Your last-minute-road-trip ride or die. I’m water-friendly, built with soft-touch handles and a comfy shoulder strap, and come prepared with a removable essentials pouch to keep valuables safe. Plus, I’m ready at a moment’s notice and can carry everyth</t>
+          <t>A honey-gold 40 oz tumbler covered in Pooh and friends, with a comfort handle, a straw lid and a base that fits the cup holder. Pick the standard box, or the gift box if it is headed to someone else's doorstep.</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr"/>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Cherry Charm</t>
+          <t>32oz Sugar Plum Fairy Tumbler</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Charm</t>
+          <t>Water bottle</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>A tiny cherry charm with a black bow, a heart and beads on a silver chain — for the bag, the keys, the phone strap or the loop of a water bottle. Small price, big personality.</t>
+          <t>Ballet pink with white ribbon bows and a pink flip-top straw lid. The Sugar Plum Fairy is the softest bottle in the lineup — 32 oz, insulated, loop-carry.</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr"/>
@@ -1071,22 +1071,22 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Snoopy Glass Cup</t>
+          <t>32oz Wicked for Good Tumbler</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Glass cup</t>
+          <t>Water bottle</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>Default Title</t>
+          <t>Emerald Green, Pink Shimmer</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>Snoopy, but make him a cup: a clear glass shaped like the world's favorite beagle, topped with a little orange beanie lid, a green scarf and a straw. The desk-drink upgrade that gets a "where did you get that" every single time.</t>
+          <t>From bubble to broomstick: Glinda's pearlescent pink shimmer or Elphaba's emerald green, on a 32 oz flip-straw bottle. Two legends, one very good bottle.</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr"/>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>GlossUp Mini™ Mini Straightener</t>
+          <t>Black Cherry Tumbler 32oz</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Hair tool</t>
+          <t>Water bottle</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>A palm-sized heated straightening brush in blush pink. Brush through, and it smooths flyaways and frizz in a couple of passes — small enough for a purse, quick enough for the ten minutes before you leave. Compact heated brush with a smooth, rounded shell Quick heat-up for touch-ups on the go Purse and carry-on sized Check the plug type for your cou</t>
+          <t>Deep burgundy from lid to base — the Black Cherry is the grown-up one. 32 oz, flip-top straw lid, carry loop, insulated for hours.</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr"/>
@@ -1141,22 +1141,22 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Camo Hoodie</t>
+          <t>Golf 30oz Bottle FreeSip</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Hoodie</t>
+          <t>Water bottle</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>XS/S, M/L, L/XL</t>
+          <t>Default Title</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>Oversized forest-camo hoodie with the red "boys lie" print across the chest. Roomy hood, kangaroo pocket, made to match the sweatpants.</t>
+          <t>Cream with a dimpled golf-ball texture and a flip-top straw lid. 30 oz, insulated, loop-carry — the one for the range, the course, or just the person who talks about their swing.</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr"/>
@@ -1176,22 +1176,22 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Women's Two Piece Lounge Set</t>
+          <t>Night Watch Tumbler 32oz</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Lounge set</t>
+          <t>Water bottle</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>Blue / S, Blue / M, Blue / L, Blue / XL, Blue / 2XL</t>
+          <t>Default Title</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>An oversized tee and matching wide-leg pants in a soft, drapey knit — the set for Sunday mornings, long flights and working from the couch. Eight colors, sizes S to 2XL. Relaxed oversized tee with side slits Wide-leg pants with an elastic waist Soft, drapey knit that does not cling Machine wash cold, lay flat to dry</t>
+          <t>Matte black with a red web that wraps the whole bottle — the Night Watch is the spooky-season bottle for people who do not do cute. 32 oz, flip-top straw lid, carry loop.</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr"/>
@@ -1211,22 +1211,22 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Harry Styles Jellycat Bunny</t>
+          <t>Owala Exclusive Cat Collage FreeSip 32 oz Water Bottle</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Plush</t>
+          <t>Water bottle</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Default Title</t>
+          <t>Pink, Green</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>A grey floppy-eared bunny with "Harry Styles" stitched on one ear and "Kiss me… all the time" and "Disco Occasion" on its paws. Soft, huggable, and very much the shelf piece for the fan in your life.</t>
+          <t>A collage of cats in hats, glasses and bows on a cream 32 oz bottle. Pink or green flip-top lid. For the person whose camera roll is 80% cat.</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr"/>
@@ -1246,12 +1246,12 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Weighted Cow Plush</t>
+          <t>Owala Exclusive Silly Goose FreeSip 32 oz Water Bottle</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Plush</t>
+          <t>Water bottle</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>A fluffy highland cow with a gentle weight inside — the plush that works like a mini weighted blanket. Rest it on your lap, your chest or your belly for a calm, grounding hug at the end of the day. Gentle, evenly distributed weight for a calming feel Ultra-soft long-pile fur with tiny horns and a fringe Great for wind-down time, study breaks and tr</t>
+          <t>Geese in scarves, geese with flowers, geese being geese — all over a powder-blue 32 oz bottle with an orange-and-pink flip-top straw lid. The bottle that makes people smile in the elevator.</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr"/>
@@ -1281,22 +1281,22 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Camo Sweatpants</t>
+          <t>Owala FreeSip</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Sweatpants</t>
+          <t>Water bottle</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>S, M, L, XL</t>
+          <t>Round we Ghost / 24oz, Round we Ghost / 32oz, Round we Ghost / 40oz, Plaid and Simple / 24oz, Plaid and Simple / 32oz</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>Forest camo sweatpants with a big red "boys lie" statement print down the leg. Relaxed fit, elastic waist, made to match the hoodie.</t>
+          <t>I’m kind of a big deal. Why? Because I invented the whole sip-or-swig thing. Hold me upright and sip through my built-in straw, or tilt me back to swig through the wide-mouth opening. But that’s not all—one push and I pop open, one push and I’m locked tight (bye bye, leaks). Basically, I’m the overachiever of water bottles, and darn proud of it.</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr"/>
@@ -1316,22 +1316,22 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>SkySoothe© - Your Passport to Elevated Comfort!</t>
+          <t>Owala FreeSip Sway</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Travel pillow</t>
+          <t>Water bottle</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Gray, Black, Pink</t>
+          <t>Tropical Mirage / 18oz, Tropical Mirage / 30oz, Tropical Mirage / 40oz, Tropical Mirage / 64oz, Very, Very Dark / 18oz</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>A memory-foam pillow that wraps and locks around your neck, so your head stays put when you doze off on the plane. Loop it, wrap it, nap. Comes with a travel bag. Memory foam that wraps around and stays in place Supports the chin so your head does not drop Rolls into the included travel bag Gray, Black or Pink</t>
+          <t>Sway is the way. Why, you ask? Well, for one, I’ve got a big ol' bucket handle that makes carrying drinks feel like a luxury, and I slide into cupholders like I was made for them (which I was). Plus, my fancy 2-in-1, sip-or-swig spout makes staying hydrated easier than ever</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr"/>
@@ -1351,22 +1351,22 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>HydroJug x Anthropologie 40 oz. Traveler</t>
+          <t>Owala FreeSip Tumbler</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>Tumbler</t>
+          <t>Water bottle</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>Default Title</t>
+          <t>Rose Quartz / 30oz, Rose Quartz / 40oz, Very Very Dark / 30oz, Very Very Dark / 40oz, Eucalyptus / 30oz</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>Cream with rows of green ribbon bows, a deep-green handle and lid. The coquette 40 oz traveler — pretty on the desk, practical in the car cup holder.</t>
+          <t>Stop searching—you’ve found me. I’m FreeSip Tumbler, the tumbler of all tumblers. With my comfy side handle, I’m easy to grab and impossible to put down. I slide perfectly into cupholders, so no more awkward juggling acts in the car. And let’s not forget my magic 2-in-1, sip-or-swig spout. I’m not just another tumbler, I’m the one you’ve been waiti</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr"/>
@@ -1386,24 +1386,20 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>PINK x HydroJug 40oz Tumbler</t>
+          <t>Owala Holiday Collection</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Tumbler</t>
+          <t>Water bottle</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Default Title</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>Bubblegum pink with a black leopard print, a matching pink handle and straw lid. The 40 oz traveler that goes from gym bag to car cup holder without spilling a drop.</t>
-        </is>
-      </c>
+          <t>Holiday Hygge / 20oz, Holiday Hygge / 24oz, Holiday Hygge / 30oz, Holiday Hygge / 32oz, Sugar Plum Fairy / 20oz</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr"/>
       <c r="G24" s="8" t="inlineStr"/>
       <c r="H24" s="8" t="inlineStr"/>
       <c r="I24" s="8" t="inlineStr"/>
@@ -1421,12 +1417,12 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Polka Dot Hydrojug 40 Oz Tumbler</t>
+          <t>Owala Mimmolo Exclusive Dog Collage FreeSip 32 oz</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>Tumbler</t>
+          <t>Water bottle</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -1436,7 +1432,7 @@
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>Cocoa brown with tiny cream polka dots, a matching handle and a straw lid. The 40 oz traveler that looks like a latte and holds a whole afternoon of ice water.</t>
+          <t>Pugs in cowboy hats, corgis in sunglasses, a dachshund in a bandana — the dog collage on a powder-blue 32 oz bottle with a lilac flip-top straw lid.</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr"/>
@@ -1456,24 +1452,20 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Sally x Jack Skellington 40oz Tumbler</t>
+          <t>Owala Soccer</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Tumbler</t>
+          <t>Water bottle</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>Default Title</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>Jack and Sally in a purple drip of stars, spiders and pumpkins, printed on a 40 oz tumbler that glows in the dark . Handle, straw lid, cup-holder base — and a moonlit glow once the porch light goes off.</t>
-        </is>
-      </c>
+          <t>Splash of Liberty, GOAL!, Steel the Ball, All American</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr"/>
       <c r="G26" s="8" t="inlineStr"/>
       <c r="H26" s="8" t="inlineStr"/>
       <c r="I26" s="8" t="inlineStr"/>
@@ -1491,22 +1483,22 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Tortoise Hydrojug 40 Oz Tumbler</t>
+          <t>Owala x Wicked Limited-Edition FreeSip</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>Tumbler</t>
+          <t>Water bottle</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Default Title</t>
+          <t>Glinda, Elphaba</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>Glossy tortoise shell in amber and black, with a black handle and lid. The 40 oz traveler that looks like your favorite sunglasses.</t>
+          <t>From bubble to broomstick, two legends unite. Glinda’s pearlescent pink shimmers with goodness. Elphaba’s emerald green sparkles with power. Together, they turn everyday hydration into something extraordinary. Magic in your hands? Or maybe it’s FreeSip®. Curious how these bottles came to life? Go behind the design.</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr"/>
@@ -1526,22 +1518,22 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Winnie The Pooh 40 oz Tumbler</t>
+          <t>Spiderman 24oz FreeSip Tumbler</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Tumbler</t>
+          <t>Water bottle</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>Standard Box, Gift Box 🎁</t>
+          <t>Default Title</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>A honey-gold 40 oz tumbler covered in Pooh and friends, with a comfort handle, a straw lid and a base that fits the cup holder. Pick the standard box, or the gift box if it is headed to someone else's doorstep.</t>
+          <t>Red and blue Spider-Man bottle in a kid-friendly 24 oz size, with a flip-top straw lid and a carry loop for the backpack. Insulated, so it is still cold at pickup.</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr"/>
@@ -1561,7 +1553,7 @@
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>32oz Sugar Plum Fairy Tumbler</t>
+          <t>Starwars Collection Limited Edition 32oz FreeSip</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
@@ -1571,12 +1563,12 @@
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>Default Title</t>
+          <t>Darth Vader, GroGu</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>Ballet pink with white ribbon bows and a pink flip-top straw lid. The Sugar Plum Fairy is the softest bottle in the lineup — 32 oz, insulated, loop-carry.</t>
+          <t>Built for long days and late nights. A 32 oz flip-straw bottle in two Star Wars looks: matte black Darth Vader with red details, or the Grogu edition. Insulated, loop-carry, cup-holder friendly.</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr"/>
@@ -1596,7 +1588,7 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>32oz Wicked for Good Tumbler</t>
+          <t>Summer Bottle Collection</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
@@ -1606,12 +1598,12 @@
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>Emerald Green, Pink Shimmer</t>
+          <t>French Picnic, Silly Goose, Tulip Time</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>From bubble to broomstick: Glinda's pearlescent pink shimmer or Elphaba's emerald green, on a 32 oz flip-straw bottle. Two legends, one very good bottle.</t>
+          <t>Three summer prints, one bottle: French Picnic (wine, cheese and cherries), Silly Goose (geese in every mood) and Tulip Time. 32 oz with a flip-top straw lid and a carry loop for the tote.</t>
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr"/>
@@ -1631,22 +1623,22 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Black Cherry Tumbler 32oz</t>
+          <t>Aqua and Green Striped 12 Oz Can Cooler</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>Water bottle</t>
+          <t>can coolers</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>Default Title</t>
+          <t>Aqua &amp; Green</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>Deep burgundy from lid to base — the Black Cherry is the grown-up one. 32 oz, flip-top straw lid, carry loop, insulated for hours.</t>
+          <t>Aqua &amp; Green Striped 12 Oz Can Cooler Keep your drink cool and your style on point with our Aqua &amp; Green Striped 12 Oz Can Cooler! The bright aqua and green stripes bring a fun pop of color to your favorite drinks, whether you’re hanging out at home or heading out for the day. Designed to fit 12 oz slim cans, this insulated can cooler is perfect fo</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr"/>
@@ -1666,22 +1658,22 @@
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Golf 30oz Bottle FreeSip</t>
+          <t>Black &amp; Pink Mini Bows Tall Can Cooler</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Water bottle</t>
+          <t>can coolers</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>Default Title</t>
+          <t>Light Pink</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>Cream with a dimpled golf-ball texture and a flip-top straw lid. 30 oz, insulated, loop-carry — the one for the range, the course, or just the person who talks about their swing.</t>
+          <t>Keep It Cute (and Cold) — The Mini Bows Slim Can Cooler The Black &amp; Pink Mini Bows Slim Can Cooler is the cutest way to keep your seltzers cold, your hands dry, and your vibe effortlessly girly. With a girly pink backdrop and playful black mini bows, this can koozie gives every poolside moment and patio happy hour a touch of coquette magic. This bo</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr"/>
@@ -1701,22 +1693,22 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Night Watch Tumbler 32oz</t>
+          <t>Black &amp; White Bows Slim Can Cooler</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>Water bottle</t>
+          <t>can coolers</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>Default Title</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>Matte black with a red web that wraps the whole bottle — the Night Watch is the spooky-season bottle for people who do not do cute. 32 oz, flip-top straw lid, carry loop.</t>
+          <t>Black &amp; White Bows Slim Can Cooler A little bow moment for your favorite drink 🎀 Our Black &amp; White Bows Slim Can Cooler is equal parts cute and classic, with a playful bow print that makes your drinkware feel instantly more fun. The insulated design fits 12 oz slim cans and helps keep your drink cool while you’re out and about. Bring it along for b</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr"/>
@@ -1736,22 +1728,22 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Owala Exclusive Cat Collage FreeSip 32 oz Water Bottle</t>
+          <t>Blue Coquette Bows Slim Can Insulator</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Water bottle</t>
+          <t>can coolers</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>Pink, Green</t>
+          <t>Light Blue</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>A collage of cats in hats, glasses and bows on a cream 32 oz bottle. Pink or green flip-top lid. For the person whose camera roll is 80% cat.</t>
+          <t>Sweet, Girly, &amp; Ice Cold: The Coquette Bow Can Cooler You’ll Love The bow-core obsession is real, and now your drink can join the trend. Meet the Blue Coquette Bows Slim Can Cooler: the cutest way to keep your seltzers cold, your hands dry, and your vibes high. With its dreamy light-blue base and delicate white bow print, this can koozie is basical</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr"/>
@@ -1771,22 +1763,22 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>Owala Exclusive Silly Goose FreeSip 32 oz Water Bottle</t>
+          <t>Blueberries Skinny Drink Cooler</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>Water bottle</t>
+          <t>can coolers</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>Default Title</t>
+          <t>Light Blue</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>Geese in scarves, geese with flowers, geese being geese — all over a powder-blue 32 oz bottle with an orange-and-pink flip-top straw lid. The bottle that makes people smile in the elevator.</t>
+          <t xml:space="preserve">Berry Cute, Berry Chilly Berry cute and ready to chill! The Blueberries Skinny Drink Cooler features a fun blueberry print that adds a fresh, playful touch to your favorite 12 oz slim can. Its insulated design helps keep your drink cool while you're lounging by the pool, spending the day outside, or enjoying a casual drink with friends. Toss it in </t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr"/>
@@ -1806,22 +1798,22 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Owala FreeSip</t>
+          <t>Brown Leopard Slim Can Cooler</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Water bottle</t>
+          <t>can coolers</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>Round we Ghost / 24oz, Round we Ghost / 32oz, Round we Ghost / 40oz, Plaid and Simple / 24oz, Plaid and Simple / 32oz</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>I’m kind of a big deal. Why? Because I invented the whole sip-or-swig thing. Hold me upright and sip through my built-in straw, or tilt me back to swig through the wide-mouth opening. But that’s not all—one push and I pop open, one push and I’m locked tight (bye bye, leaks). Basically, I’m the overachiever of water bottles, and darn proud of it.</t>
+          <t xml:space="preserve">Brown Leopard Slim Can Cooler Your drink deserves a little attitude. Our Brown Leopard Slim Can Cooler brings the timeless leopard print trend straight to your favorite beverage, making it an easy accessory for anyone who likes their essentials with a little personality. The insulated design is made to fit 12 oz slim cans and helps keep your drink </t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr"/>
@@ -1841,22 +1833,22 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>Owala FreeSip Sway</t>
+          <t>Cow Print Can Cooler Koozie</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Water bottle</t>
+          <t>can coolers</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>Tropical Mirage / 18oz, Tropical Mirage / 30oz, Tropical Mirage / 40oz, Tropical Mirage / 64oz, Very, Very Dark / 18oz</t>
+          <t>White</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>Sway is the way. Why, you ask? Well, for one, I’ve got a big ol' bucket handle that makes carrying drinks feel like a luxury, and I slide into cupholders like I was made for them (which I was). Plus, my fancy 2-in-1, sip-or-swig spout makes staying hydrated easier than ever</t>
+          <t>Your Summer Sidekick: Cow Print Slim Can Cooler for Every Adventure If you’re the girl who brings the vibes and the beverages, this one’s for you. Our Cow Print Slim Can Cooler is your ticket to keeping drinks cold and selfies cute all season long. Designed for the seltzer-loving, road-tripping, poolside-chilling kind of girl, this can koozie turns</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr"/>
@@ -1876,22 +1868,22 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Owala FreeSip Tumbler</t>
+          <t>Fresh Picked Fruits Slim Can Cooler</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Water bottle</t>
+          <t>can coolers</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>Rose Quartz / 30oz, Rose Quartz / 40oz, Very Very Dark / 30oz, Very Very Dark / 40oz, Eucalyptus / 30oz</t>
+          <t>Cream</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>Stop searching—you’ve found me. I’m FreeSip Tumbler, the tumbler of all tumblers. With my comfy side handle, I’m easy to grab and impossible to put down. I slide perfectly into cupholders, so no more awkward juggling acts in the car. And let’s not forget my magic 2-in-1, sip-or-swig spout. I’m not just another tumbler, I’m the one you’ve been waiti</t>
+          <t>Fresh Picked &amp; Ready to Sip Fresh-picked style meets your favorite cold drink! The Fresh Picked Fruits Slim Can Cooler is covered in a colorful fruit-inspired print that brings a fun, cheerful feel to any occasion. Designed for 12 oz slim cans, this insulated cooler helps keep your drink chilled while adding a playful pop of personality to your eve</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr"/>
@@ -1911,20 +1903,24 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Owala Holiday Collection</t>
+          <t>Groovy Multicolored Flowers Slim Can Koozie</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Water bottle</t>
+          <t>can coolers</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>Holiday Hygge / 20oz, Holiday Hygge / 24oz, Holiday Hygge / 30oz, Holiday Hygge / 32oz, Sugar Plum Fairy / 20oz</t>
-        </is>
-      </c>
-      <c r="F39" s="8" t="inlineStr"/>
+          <t>Light Pink</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>Bright Drinks, Good Times — The Groovy Flower Insulated Can Cooler Bring on the flower power, babe! The Groovy Multicolored Flowers Slim Can Cooler is everything your summer lineup needs. Designed for the girls who love good times, bold prints, and cold drinks, this insulated can cooler keeps your seltzer chilled and your hands dry from the first s</t>
+        </is>
+      </c>
       <c r="G39" s="8" t="inlineStr"/>
       <c r="H39" s="8" t="inlineStr"/>
       <c r="I39" s="8" t="inlineStr"/>
@@ -1942,22 +1938,22 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Owala Mimmolo Exclusive Dog Collage FreeSip 32 oz</t>
+          <t>Light Blue Scalloped 12 Oz Can Cooler</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Water bottle</t>
+          <t>can coolers</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>Default Title</t>
+          <t>Light Blue</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>Pugs in cowboy hats, corgis in sunglasses, a dachshund in a bandana — the dog collage on a powder-blue 32 oz bottle with a lilac flip-top straw lid.</t>
+          <t>A Little Scallop, A Lot of Chill Give your favorite drink a cute little upgrade with the Light Blue Scalloped 12 Oz Can Cooler. Featuring a playful scalloped design in a soft light blue, this insulated can cooler is the perfect mix of pretty and practical. It keeps your 12 oz slim cans chilled while adding a fun touch to pool days, patio hangs, tai</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr"/>
@@ -1977,20 +1973,24 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>Owala Soccer</t>
+          <t>Light Blue and Navy Striped Tall Can Cooler</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Water bottle</t>
+          <t>can coolers</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>Splash of Liberty, GOAL!, Steel the Ball, All American</t>
-        </is>
-      </c>
-      <c r="F41" s="8" t="inlineStr"/>
+          <t>Light Blue and Navy</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>Sippin’ by the Sea — The Light Blue &amp; Navy Striped Insulated Can Cooler Beach days, boat rides, and backyard hangs just got cooler. The Light Blue &amp; Navy Striped Slim Can Cooler is your must-have summer accessory. It's equal parts classic and cute, giving major coastal-core energy. Made from stainless steel and built with double-wall insulation, th</t>
+        </is>
+      </c>
       <c r="G41" s="8" t="inlineStr"/>
       <c r="H41" s="8" t="inlineStr"/>
       <c r="I41" s="8" t="inlineStr"/>
@@ -2008,22 +2008,22 @@
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Owala x Wicked Limited-Edition FreeSip</t>
+          <t>Light Pink Scalloped Slim Can Cooler Drinks</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Water bottle</t>
+          <t>can coolers</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>Glinda, Elphaba</t>
+          <t>Light Pink</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>From bubble to broomstick, two legends unite. Glinda’s pearlescent pink shimmers with goodness. Elphaba’s emerald green sparkles with power. Together, they turn everyday hydration into something extraordinary. Magic in your hands? Or maybe it’s FreeSip®. Curious how these bottles came to life? Go behind the design.</t>
+          <t>Pretty in Pink &amp; Ready to Chill Pretty in pink and ready for a cold drink! The Light Pink Scalloped Slim Can Cooler brings a sweet, feminine touch to your drink lineup with its soft pink color and playful scalloped pattern. Designed to keep your favorite 12 oz slim can nice and chilled, it's an easy go-to for girls' nights, weekend getaways, backya</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr"/>
@@ -2043,22 +2043,22 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>Spiderman 24oz FreeSip Tumbler</t>
+          <t>Navy and Pink Striped Slim Can Cooler</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Water bottle</t>
+          <t>can coolers</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>Default Title</t>
+          <t>Navy &amp; Pink</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>Red and blue Spider-Man bottle in a kid-friendly 24 oz size, with a flip-top straw lid and a carry loop for the backpack. Insulated, so it is still cold at pickup.</t>
+          <t>Navy &amp; Pink Striped Slim Can Cooler Keep your drink cool with a little extra style! Our Navy &amp; Pink Striped Slim Can Cooler features bold navy and playful pink stripes for a fun pop of color that makes every sip more fun. Made to fit 12 oz slim cans, this insulated can cooler is perfect for girls' nights, game days, pool days, tailgates, backyard h</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr"/>
@@ -2078,22 +2078,22 @@
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Starwars Collection Limited Edition 32oz FreeSip</t>
+          <t>Pastel Leopard Can Cooler Beer Can</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Water bottle</t>
+          <t>can coolers</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>Darth Vader, GroGu</t>
+          <t>Pastel</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>Built for long days and late nights. A 32 oz flip-straw bottle in two Star Wars looks: matte black Darth Vader with red details, or the Grogu edition. Insulated, loop-carry, cup-holder friendly.</t>
+          <t>Introducing the "Pastel Leopard Can Cooler" - your stylish sidekick for keeping drinks chill and refreshing, designed exclusively by Mimmolo. This insulated beer can holder is not just a functional accessory but a fashion statement in itself. Picture yourself sipping your favorite beverage in style with the trendy pastel leopard print, adding a tou</t>
         </is>
       </c>
       <c r="G44" s="8" t="inlineStr"/>
@@ -2113,22 +2113,22 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>Summer Bottle Collection</t>
+          <t>Peach Scalloped Slim Koozie Can Cooler</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Water bottle</t>
+          <t>can coolers</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>French Picnic, Silly Goose, Tulip Time</t>
+          <t>Peach</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>Three summer prints, one bottle: French Picnic (wine, cheese and cherries), Silly Goose (geese in every mood) and Tulip Time. 32 oz with a flip-top straw lid and a carry loop for the tote.</t>
+          <t>Peachy Sips Start Here A little peachy, a little playful, and totally ready for your next drink break. The Peach Scalloped Slim Can Cooler adds a fun pop of color to your favorite 12 oz slim can while helping keep it cool from the first sip to the last. Its cheerful peach shade and scalloped design make it an easy accessory for sunny days, parties,</t>
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr"/>
@@ -2148,22 +2148,22 @@
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Black Woven Bucket Handbag</t>
+          <t>Pink and Hot Pink Striped Slim Can Cooler</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>bucket bags</t>
+          <t>can coolers</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Pink and Hot Pink</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>Back to Black: Your Everyday Bucket Bag Just Got Better Meet your new go-to: the Black Bucket Crossbody Bag. Whether you're running errands, heading to class, or catching a flight, this bag is lightweight, versatile, and effortlessly cute. The soft neoprene fabric gives it a sporty edge, while the crossbody strap keeps things hands-free and functio</t>
+          <t>Hot Pink Summer Energy — The Striped Can Koozie You’ll Love Because your drink deserves to be as cute as your outfit Meet the Pink and Hot Pink Striped Insulated Can Cooler, the ultimate warm-weather essential for seltzer lovers, brunch girls, and beach babes everywhere. Designed with double-wall stainless steel insulation, this can koozie keeps yo</t>
         </is>
       </c>
       <c r="G46" s="8" t="inlineStr"/>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>Aqua and Green Striped 12 Oz Can Cooler</t>
+          <t>Pink and Orange Striped Slim Can Cooler</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
@@ -2193,12 +2193,12 @@
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>Aqua &amp; Green</t>
+          <t>Pink &amp; Orange</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>Aqua &amp; Green Striped 12 Oz Can Cooler Keep your drink cool and your style on point with our Aqua &amp; Green Striped 12 Oz Can Cooler! The bright aqua and green stripes bring a fun pop of color to your favorite drinks, whether you’re hanging out at home or heading out for the day. Designed to fit 12 oz slim cans, this insulated can cooler is perfect fo</t>
+          <t>Pink &amp; Orange Striped Slim Can Cooler Make every sip a little more fun with our Pink &amp; Orange Striped Slim Can Cooler! Bright, playful, and full of personality, this colorful can cooler is the perfect accessory for keeping your favorite drink cool in style. Designed to fit 12 oz slim cans, it’s ready for pool days, girls' nights, tailgates, beach t</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Black &amp; Pink Mini Bows Tall Can Cooler</t>
+          <t>Pink and Wine Striped 12 Oz Can Cooler</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>Light Pink</t>
+          <t>Pink &amp; Wine</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>Keep It Cute (and Cold) — The Mini Bows Slim Can Cooler The Black &amp; Pink Mini Bows Slim Can Cooler is the cutest way to keep your seltzers cold, your hands dry, and your vibe effortlessly girly. With a girly pink backdrop and playful black mini bows, this can koozie gives every poolside moment and patio happy hour a touch of coquette magic. This bo</t>
+          <t>Pink &amp; Wine Striped 12 Oz Can Cooler Sip in style with our Pink &amp; Wine Striped 12 Oz Can Cooler! The playful pink and wine stripes add a fun pop of color while the insulated design helps keep your drink cool from the first sip to the last. Made to fit 12 oz slim cans, this cute can cooler is perfect for girls' nights, game days, pool days, tailgate</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr"/>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>Black &amp; White Bows Slim Can Cooler</t>
+          <t>Roses Slim Can Cooler Koozie</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Light Pink</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>Black &amp; White Bows Slim Can Cooler A little bow moment for your favorite drink 🎀 Our Black &amp; White Bows Slim Can Cooler is equal parts cute and classic, with a playful bow print that makes your drinkware feel instantly more fun. The insulated design fits 12 oz slim cans and helps keep your drink cool while you’re out and about. Bring it along for b</t>
+          <t>Stop &amp; Sip the Roses Bring a little floral fun to your next happy hour with the Roses Slim Can Cooler. Covered in a pretty rose-inspired print, this can cooler turns your everyday drink into a cute accessory. The insulated design helps keep 12 oz slim cans cool, making it perfect for brunch with the girls, outdoor parties, concerts, tailgates, or a</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr"/>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Blue Coquette Bows Slim Can Insulator</t>
+          <t>Zesty Lemons Slim Can Cooler</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>Sweet, Girly, &amp; Ice Cold: The Coquette Bow Can Cooler You’ll Love The bow-core obsession is real, and now your drink can join the trend. Meet the Blue Coquette Bows Slim Can Cooler: the cutest way to keep your seltzers cold, your hands dry, and your vibes high. With its dreamy light-blue base and delicate white bow print, this can koozie is basical</t>
+          <t>Lemonade, Laughs &amp; Long Weekends — The Cutest Can Cooler Ever When life gives you lemons… you chill your drink in them. The Zesty Lemons Slim Can Cooler Insulator is your new must-have for sunny days, road trips, and every happy hour in between. Designed with the girliest summer vibe, this can koozie keeps your drink cool and your hands dry while l</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr"/>
@@ -2323,22 +2323,22 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>Blueberries Skinny Drink Cooler</t>
+          <t>American Bows 38 Oz Tumbler with Handle</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>can coolers</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>Light Blue</t>
+          <t>White Flag Bows</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Berry Cute, Berry Chilly Berry cute and ready to chill! The Blueberries Skinny Drink Cooler features a fun blueberry print that adds a fresh, playful touch to your favorite 12 oz slim can. Its insulated design helps keep your drink cool while you're lounging by the pool, spending the day outside, or enjoying a casual drink with friends. Toss it in </t>
+          <t>Show your American pride while drinking your daily dose of water with the adorable American Bows tumbler. This 38 ounce cup is exactly what you need to carry around this election season!¬† 38 ounces includes reusable plastic straw all-day chill or heat stainless steel interior dishwasher safe screw-on plastic top with straw opening adjustable straw</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr"/>
@@ -2358,22 +2358,22 @@
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Brown Leopard Slim Can Cooler</t>
+          <t>American Flag &amp; Lips 38 Oz Tumbler Cup</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>can coolers</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>White and Red Lips</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brown Leopard Slim Can Cooler Your drink deserves a little attitude. Our Brown Leopard Slim Can Cooler brings the timeless leopard print trend straight to your favorite beverage, making it an easy accessory for anyone who likes their essentials with a little personality. The insulated design is made to fit 12 oz slim cans and helps keep your drink </t>
+          <t>Get ready to pucker up for patriotism with the American Flag &amp; Lips 38 Oz Tumbler Cup from Mimmolo. This striking white tumbler is not just a cup; it's a celebration of style, stars, and stripes. Emblazoned with American flag stripes, mini stars, and playful red and blue lips, this 38-ounce tumbler is the perfect accessory for those who want to sho</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr"/>
@@ -2393,22 +2393,22 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>Cow Print Can Cooler Koozie</t>
+          <t>American Happy Face 38 Oz Tumbler Cup w/ Handle</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>can coolers</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>White USA</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>Your Summer Sidekick: Cow Print Slim Can Cooler for Every Adventure If you’re the girl who brings the vibes and the beverages, this one’s for you. Our Cow Print Slim Can Cooler is your ticket to keeping drinks cold and selfies cute all season long. Designed for the seltzer-loving, road-tripping, poolside-chilling kind of girl, this can koozie turns</t>
+          <t>Get ready to express your patriotic spirit in every sip with the American Happy Face 38 Oz Tumbler Cup w/ Handle, exclusively from Mimmolo.com. This large and stylish tumbler is not just a cup; it's a celebration of American pride and positivity. Featuring a vibrant design of happy faces adorned with the iconic stars and stripes, this tumbler is th</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr"/>
@@ -2428,22 +2428,22 @@
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Fresh Picked Fruits Slim Can Cooler</t>
+          <t>Aqua and Green Striped 30 Oz Cabana Tumbler</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>can coolers</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>Cream</t>
+          <t>Aqua and Green</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>Fresh Picked &amp; Ready to Sip Fresh-picked style meets your favorite cold drink! The Fresh Picked Fruits Slim Can Cooler is covered in a colorful fruit-inspired print that brings a fun, cheerful feel to any occasion. Designed for 12 oz slim cans, this insulated cooler helps keep your drink chilled while adding a playful pop of personality to your eve</t>
+          <t>30 oz Travel Tumbler Cup in Aqua + Green Stripes If you’ve been waiting for a sign to upgrade your hydration game, this is it. Our aqua and green striped tumbler cup is here to add a splash of fun, function, and bold personality to your everyday routine. With a vibrant teal-and-green striped design, this 30 oz travel tumbler cup is giving total poo</t>
         </is>
       </c>
       <c r="G54" s="8" t="inlineStr"/>
@@ -2463,22 +2463,22 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>Groovy Multicolored Flowers Slim Can Koozie</t>
+          <t>Black &amp; Pink Mini Coquette Bows 38 Oz Tumbler w/ Handle</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>can coolers</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>Light Pink</t>
+          <t>Black and Pink Bows</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>Bright Drinks, Good Times — The Groovy Flower Insulated Can Cooler Bring on the flower power, babe! The Groovy Multicolored Flowers Slim Can Cooler is everything your summer lineup needs. Designed for the girls who love good times, bold prints, and cold drinks, this insulated can cooler keeps your seltzer chilled and your hands dry from the first s</t>
+          <t xml:space="preserve">Pretty in Pink: Sip in Style with Our Pink Bow Tumbler Indulge in the hottest trend of the season with the pink bow tumbler exclusively from Mimmolo. Bows are taking the fashion world by storm, and this stainless steel tumbler cup is the epitome of coquettish charm, making it the perfect gift for trendsetters and style enthusiasts. Picture this: a </t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr"/>
@@ -2498,22 +2498,22 @@
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Light Blue Scalloped 12 Oz Can Cooler</t>
+          <t>Black &amp; White Bows All Over Drink Tumbler Cup</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>can coolers</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>Light Blue</t>
+          <t>Black and White Bows</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>A Little Scallop, A Lot of Chill Give your favorite drink a cute little upgrade with the Light Blue Scalloped 12 Oz Can Cooler. Featuring a playful scalloped design in a soft light blue, this insulated can cooler is the perfect mix of pretty and practical. It keeps your 12 oz slim cans chilled while adding a fun touch to pool days, patio hangs, tai</t>
+          <t>A Bow Lover's Dream Tumbler is Here Sipping has never looked so chic. This Black &amp; White Bows Tumbler Cup gives you the perfect mix of elegance and playfulness. Made with durable stainless steel, it keeps your coffee hot and your look even hotter. The bold bow pattern is giving coquette queen energy, and we are here for it! Whether you're headed to</t>
         </is>
       </c>
       <c r="G56" s="8" t="inlineStr"/>
@@ -2533,22 +2533,22 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>Light Blue and Navy Striped Tall Can Cooler</t>
+          <t>Black Coffee 40 Oz Tumbler with Handle</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>can coolers</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>Light Blue and Navy</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>Sippin’ by the Sea — The Light Blue &amp; Navy Striped Insulated Can Cooler Beach days, boat rides, and backyard hangs just got cooler. The Light Blue &amp; Navy Striped Slim Can Cooler is your must-have summer accessory. It's equal parts classic and cute, giving major coastal-core energy. Made from stainless steel and built with double-wall insulation, th</t>
+          <t>Elevate your daily coffee routine with our Black Coffee 40 Oz Tumbler with Handle. Designed with style and practicality in mind, this sleek black tumbler is the perfect companion for coffee-loving men who appreciate both form and function. With its generous 40 Oz capacity, you can enjoy your favorite hot or iced beverages throughout the day, keepin</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr"/>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Light Pink Scalloped Slim Can Cooler Drinks</t>
+          <t>Black/White Cow Print Insulated Tumbler Cup with Handle</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>can coolers</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>Light Pink</t>
+          <t>Black and White Cow</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>Pretty in Pink &amp; Ready to Chill Pretty in pink and ready for a cold drink! The Light Pink Scalloped Slim Can Cooler brings a sweet, feminine touch to your drink lineup with its soft pink color and playful scalloped pattern. Designed to keep your favorite 12 oz slim can nice and chilled, it's an easy go-to for girls' nights, weekend getaways, backya</t>
+          <t>Get ready to ride off into the wild, wild west with Mimmolo's Cow Print 40 Oz Tumbler! This stainless steel tumbler is the perfect companion for fans of all things western. Adorned with a gorgeous cow print black and white pattern, you'll be ready to yee haw your way in style. The 40 oz tumbler features a convenient cup handle for you to grab onto,</t>
         </is>
       </c>
       <c r="G58" s="8" t="inlineStr"/>
@@ -2603,22 +2603,22 @@
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>Navy and Pink Striped Slim Can Cooler</t>
+          <t>Blue Insulated Tumbler Cup w/ Handle</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>can coolers</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>Navy &amp; Pink</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>Navy &amp; Pink Striped Slim Can Cooler Keep your drink cool with a little extra style! Our Navy &amp; Pink Striped Slim Can Cooler features bold navy and playful pink stripes for a fun pop of color that makes every sip more fun. Made to fit 12 oz slim cans, this insulated can cooler is perfect for girls' nights, game days, pool days, tailgates, backyard h</t>
+          <t>A new addition to the solid tumblers: a cool blue that matches the blue jean day. Sometimes you just need the basics. 40 ounces includes reusable plastic straw all-day chill or heat stainless steel interior dishwasher safe screw-on plastic top with straw opening adjustable straw cover for easy travel easy-to-hold handle fits in car cup holder (3" d</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr"/>
@@ -2638,22 +2638,22 @@
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Pastel Leopard Can Cooler Beer Can</t>
+          <t>Bride Red Drawings 38 Oz Tumbler</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>can coolers</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>Pastel</t>
+          <t>Light Pink Bride</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>Introducing the "Pastel Leopard Can Cooler" - your stylish sidekick for keeping drinks chill and refreshing, designed exclusively by Mimmolo. This insulated beer can holder is not just a functional accessory but a fashion statement in itself. Picture yourself sipping your favorite beverage in style with the trendy pastel leopard print, adding a tou</t>
+          <t>Ready to sip in style on your Big Day? Let us introduce you to Mimmolo's new Bride Red Drawings 38 Oz Tumbler! This tumbler is everything you need to celebrate the bride-to-be in style! Whether you're planning the ultimate bachelorette trip or treating yourself as the bride, this trendy stainless steel tumbler is your new best friend. With its bold</t>
         </is>
       </c>
       <c r="G60" s="8" t="inlineStr"/>
@@ -2673,22 +2673,22 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>Peach Scalloped Slim Koozie Can Cooler</t>
+          <t>Cabana 38 Oz Tumbler with Handle (Pink and Orange Striped)</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>can coolers</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>Peach</t>
+          <t>Pink and Orange</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>Peachy Sips Start Here A little peachy, a little playful, and totally ready for your next drink break. The Peach Scalloped Slim Can Cooler adds a fun pop of color to your favorite 12 oz slim can while helping keep it cool from the first sip to the last. Its cheerful peach shade and scalloped design make it an easy accessory for sunny days, parties,</t>
+          <t>Hydration Upgrade: Pink + Orange Striped 38 oz Tumbler Jug Let’s be real — your hydration routine deserves an upgrade, and this pink + orange striped tumbler cup is here to deliver. At 38 oz, it’s oversized enough to keep you fueled through long workdays, workouts, or poolside lounging without constant refills. And it’s not just big — it’s brillian</t>
         </is>
       </c>
       <c r="G61" s="8" t="inlineStr"/>
@@ -2708,22 +2708,22 @@
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Pink and Hot Pink Striped Slim Can Cooler</t>
+          <t>Camo Print Tumbler Cup with Straw</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>can coolers</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>Pink and Hot Pink</t>
+          <t>Camo</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>Hot Pink Summer Energy — The Striped Can Koozie You’ll Love Because your drink deserves to be as cute as your outfit Meet the Pink and Hot Pink Striped Insulated Can Cooler, the ultimate warm-weather essential for seltzer lovers, brunch girls, and beach babes everywhere. Designed with double-wall stainless steel insulation, this can koozie keeps yo</t>
+          <t>Hey there, guys! Say hello to the Camo Print Tumbler Cup with Straw, the must-have accessory for the modern man. This rugged and stylish tumbler is designed to keep up with your active lifestyle while adding a touch of cool camo vibes to your everyday routine. Featuring a sleek camo print, this tumbler is the perfect blend of fashion and functional</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr"/>
@@ -2743,22 +2743,22 @@
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>Pink and Orange Striped Slim Can Cooler</t>
+          <t>Dainty Florals Pink 38 Oz Tumbler Cup</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>can coolers</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>Pink &amp; Orange</t>
+          <t>Light Pink and Blue Flowers</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>Pink &amp; Orange Striped Slim Can Cooler Make every sip a little more fun with our Pink &amp; Orange Striped Slim Can Cooler! Bright, playful, and full of personality, this colorful can cooler is the perfect accessory for keeping your favorite drink cool in style. Designed to fit 12 oz slim cans, it’s ready for pool days, girls' nights, tailgates, beach t</t>
+          <t>Stay hydrated in style with the Dainty Florals Pink 38 Oz Tumbler! This adorable pink tumbler isn’t just a pretty face; it’s got all the features you need to make drinking water a total vibe. With a sturdy handle for easy carrying, it fits right in your car cup holder (because yes, you can have both style and function). And don’t worry about the cl</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr"/>
@@ -2778,22 +2778,22 @@
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Pink and Wine Striped 12 Oz Can Cooler</t>
+          <t>Deer All Over Black Tumbler for Men</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>can coolers</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>Pink &amp; Wine</t>
+          <t>Black Deer</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t>Pink &amp; Wine Striped 12 Oz Can Cooler Sip in style with our Pink &amp; Wine Striped 12 Oz Can Cooler! The playful pink and wine stripes add a fun pop of color while the insulated design helps keep your drink cool from the first sip to the last. Made to fit 12 oz slim cans, this cute can cooler is perfect for girls' nights, game days, pool days, tailgate</t>
+          <t>Hey, guys! Looking for a stylish tumbler that combines rugged charm with sleek design? Look no further than the Deer All Over Black Tumbler for Men, available at Mimmolo.com. This black tumbler exudes a confident vibe with its metallic silver deer design, adding a touch of sophistication to your daily routine. Crafted with care and attention to det</t>
         </is>
       </c>
       <c r="G64" s="8" t="inlineStr"/>
@@ -2813,22 +2813,22 @@
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>Roses Slim Can Cooler Koozie</t>
+          <t>Fall Bears 38 Oz Tumbler with Lid Handle</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>can coolers</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>Light Pink</t>
+          <t>Light Blue Teddy Bears</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>Stop &amp; Sip the Roses Bring a little floral fun to your next happy hour with the Roses Slim Can Cooler. Covered in a pretty rose-inspired print, this can cooler turns your everyday drink into a cute accessory. The insulated design helps keep 12 oz slim cans cool, making it perfect for brunch with the girls, outdoor parties, concerts, tailgates, or a</t>
+          <t>Sips and Snuggles: Your Cozy Bear Tumbler Cup Cuddle up with your new favorite tumbler cup! The Fall Bears 38 oz Tumbler is the definition of cozy girl energy, featuring an adorable teddy bear print, sturdy handle, and secure lid. It’s the ultimate companion for pumpkin patches, cozy couch hangs, and your never-ending to-do list. Whether you’re run</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr"/>
@@ -2848,22 +2848,22 @@
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Zesty Lemons Slim Can Cooler</t>
+          <t>Fishing Lures Tumbler Cup with Handle</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>can coolers</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>Light Blue</t>
+          <t>Black Fish</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>Lemonade, Laughs &amp; Long Weekends — The Cutest Can Cooler Ever When life gives you lemons… you chill your drink in them. The Zesty Lemons Slim Can Cooler Insulator is your new must-have for sunny days, road trips, and every happy hour in between. Designed with the girliest summer vibe, this can koozie keeps your drink cool and your hands dry while l</t>
+          <t>Reel in the perfect gift for the angler in your life with our Fishing Lures Tumbler Cup. Designed for the outdoorsman who cherishes every moment by the water, this sleek black tumbler features an array of vibrant fishing lures. It's not just a drink holder; it's an expression of passion for fishing. Crafted with durable stainless steel, this tumble</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr"/>
@@ -2883,12 +2883,12 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>Cherry Bows Coin Purse Bag</t>
+          <t>Groovy Multicolored Flowers Tumbler Cup</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>coin purses</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>Cute Cherry Bow Bag Charm for the Coquette Girl Cherry-picking the perfect accessory? You just found it! Meet our Cherry Bows Coin Purse, the sweetest Bag Charm for every coquette-inspired look. This adorable mini purse combines charm and function. It's a girly essential for anyone obsessed with bows, blush tones, and all things pretty. Made from s</t>
+          <t>Sip in Full Color — The Groovy Retro Stainless Steel Tumbler If sunshine had a drink cup, this would be it. The Groovy Multicolored Flowers Tumbler Cup brings all the retro-flower-power vibes to your daily sips, whether you’re lounging by the pool, running errands, or vibing through a summer road trip with the windows down. Packed with bright color</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr"/>
@@ -2918,22 +2918,22 @@
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Green Pear Coin Pouch Keychain</t>
+          <t>In My Cheer Era 38 Oz Tumbler with Lid Handle</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>coin purses</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Pink Cheer</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cute Pear-Shaped Mini Coin Purse This one’s pear-fection! Our Green Pear Mini Coin Purse is the ultimate Bag Charm for anyone who loves a pop of color and personality in their accessories. Made from vegan leather with gold-tone hardware, it’s cute yet functional. The zip closure keeps your small essentials safe while the vibrant pear design adds a </t>
+          <t>Show off your cheer spirit, on and off the mat. Mimmolo's "In My Cheer Era" tumbler is the ultimate accessory for cheerleaders who need to stay hydrated during their busy schedules. With a convenient top lid handle and a side handle, you can easily grab it while practicing your stunts or cheering on your team. Plus, it fits perfectly in a cup holde</t>
         </is>
       </c>
       <c r="G68" s="8" t="inlineStr"/>
@@ -2953,22 +2953,22 @@
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>Heart Coin Purse Keychain</t>
+          <t>Jug Tumbler Handle Lid Replacements</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>coin purses</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>Hot Pink</t>
+          <t>White, Light Pink, Pink, Green</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>Hot Pink Happiness: A Coin Purse Keychain That Brings the Fun Our Hot Pink Heart Coin Purse Keychain is proof that the tiniest accessory can be the most fun. Made in a bold hot pink shade, this heart-shaped cutie doubles as both a statement-making keychain and a practical little pouch for coins, jewelry, or other mini must-haves. Clip it to your pu</t>
+          <t>Screw-in top Lid fits on our 40 oz tumblers and 38 oz tumblers Try our unique ridged tumbler lids or our classic clear lids ! * straw sold separately</t>
         </is>
       </c>
       <c r="G69" s="8" t="inlineStr"/>
@@ -2988,22 +2988,22 @@
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Pineapple Bag Charm</t>
+          <t>Light Blue and Navy Striped 30 Oz Tumbler Cup</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>coin purses</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Light Blue and Navy</t>
         </is>
       </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
-          <t>Tropic Like It’s Hot: The Cutest Coin Purse Ever! Say aloha to your new favorite accessory! Our Pineapple Bag Charm is the cutest way to keep your essentials close while adding a tropical twist to any outfit. This fun Bag Keychain doubles as a Coin Purse, making it a must-have for summer adventures, vacations, or everyday errands. Made from soft ve</t>
+          <t>Standout Light Blue and Navy Striped Tumbler Cup for On-the-Go Style Hydration just got a major upgrade. Our blue and navy striped tumbler cup is the ultimate mix of bold design, everyday function, and “yes, I need that” energy. Made for the girl who wants her morning iced latte to stay cold until her afternoon conference call, this cute 30 oz trav</t>
         </is>
       </c>
       <c r="G70" s="8" t="inlineStr"/>
@@ -3023,22 +3023,22 @@
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>Red Apple Coin Zipper Purse</t>
+          <t>Light Blue and Navy Striped Tumbler With Handle</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>coin purses</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Light Blue and Navy</t>
         </is>
       </c>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>You’re the Apple of My Eye Coin Purse Add a little sweetness to your style! Our Red Apple Coin Purse is the perfect mix of cute and practical. Designed as both a Bag Keychain and a Coin Purse, it’s your new go-to for holding coins, gloss, or earbuds while looking totally on trend. Made from soft vegan leather with gold hardware and a zipper closure</t>
+          <t xml:space="preserve">Bold Blue 38 oz Striped Tumbler Cup with Straw Not all tumblers are created equal — and this one proves it. Our 38 oz blue striped tumbler cup is designed for people who want their drinkware to stand out while still delivering all the function they need. With bold navy-and-light blue stripes, it’s not just a tumbler — it’s a style statement you’ll </t>
         </is>
       </c>
       <c r="G71" s="8" t="inlineStr"/>
@@ -3058,22 +3058,22 @@
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Strawberry Coin Holder Bag Charm</t>
+          <t>Lobsters Tumbler Cup</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>coin purses</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>Hot Pink</t>
+          <t>Pink</t>
         </is>
       </c>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t>The Strawberry Bag Charm That’s Equal Parts Girly and Functional Your handbag just found its cutest sidekick with the Strawberry Coin Purse Keychain. Small but statement-making, this fruit-inspired accessory instantly brings summer vibes to any look. Clip it to your purse, backpack, or beach tote and let the pop of pink and green do all the talking</t>
+          <t>Beachy and Bright Lobster Print Travel Tumbler If you love a good coastal moment, the Lobsters Tumbler Cup is about to become your new warm-weather favorite. Designed with a bold, bright lobster print and crafted for long days in the sun, this tumbler with straw brings a fun, summery touch to every sip. It blends beach-town energy with everyday fun</t>
         </is>
       </c>
       <c r="G72" s="8" t="inlineStr"/>
@@ -3093,22 +3093,22 @@
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>Sweet Orange Coin Pouch Keychain</t>
+          <t>Lucky Girl Western 38 Oz Tumbler</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>coin purses</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Lucky Mint</t>
         </is>
       </c>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>Small but Juicy: The Coin Purse Keychain That Goes Everywhere Your bag just got a whole lot sweeter thanks to the Sweet Orange Coin Purse Keychain. Small but mighty, this citrus-inspired bag charm is the perfect blend of playful and practical. Attach it as a keychain to your tote or purse for a pop of color, or use it to stash your coins, lip balm,</t>
+          <t>Calling all Nashville-loving babes! This western-inspired 38 oz. stainless steel tumbler features a light blue background with trendy illustrations, including rainbows, dice, cowboy boots, and horseshoes, giving off a cool, carefree cowgirl vibe. Pair it with a matching trucker hat or accessories for a complete look that will have people saying, "O</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr"/>
@@ -3128,22 +3128,22 @@
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>Zesty Lemon Coin Purse Keychain</t>
+          <t>Mahjong Pieces Hydration Tumbler</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>coin purses</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Light Pink</t>
         </is>
       </c>
       <c r="F74" s="8" t="inlineStr">
         <is>
-          <t>Citrus-Inspired Coin Purse – The Cutest Bag Charm Ever! When life gives you lemons… accessorize! Our Zesty Lemon Coin Purse is the perfect pop of color your bag’s been missing. Equal parts adorable and functional, this sunny Bag Charm Coin Purse brings a dose of dopamine to your everyday routine. Made from high-quality vegan leather with a smooth z</t>
+          <t>Mahjong Lover Tumbler Cup for Everyday If mahjong night is your personality and your group chat is always planning the next game, this Mimmolo tumbler belongs to you. The Mahjong Pieces Flip Top Tumbler brings that fun, social energy into your everyday routine. Featuring a playful mix of tiles, florals, and girly details, it feels niche in the best</t>
         </is>
       </c>
       <c r="G74" s="8" t="inlineStr"/>
@@ -3163,22 +3163,22 @@
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>Gray Woven Cute Crossbody Bag</t>
+          <t>Men's Navy Water Tumbler Cup</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>crossbodies</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>Navy</t>
         </is>
       </c>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>The Gray Crossbody That Gets It Right Every Time This is the bag that's always there for you‚ and looks good with everything. Our gray woven neoprene crossbody is as cute as it is convenient, with a textured finish that feels a little sporty, a little luxe, and a whole lot wearable. The shade? A soft, chic neutral that works whether you're in a mat</t>
+          <t>Hey guys! Introducing the ultimate hydration solution for the modern man - the Men's Navy Water Tumbler Cup. Designed to keep you refreshed and hydrated throughout the day, this sleek navy blue tumbler is a game-changer when it comes to staying cool, calm, and collected. With its generous 40 Oz capacity, this tumbler has got your hydration needs co</t>
         </is>
       </c>
       <c r="G75" s="8" t="inlineStr"/>
@@ -3198,22 +3198,22 @@
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>Black &amp; White Coquette Bows All Over Makeup Bag</t>
+          <t>Multicolored Coquette Bows 38 Oz Tumbler w/ Handle</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>makeup bags</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>Black and White Bows</t>
+          <t>Multicolored Bows</t>
         </is>
       </c>
       <c r="F76" s="8" t="inlineStr">
         <is>
-          <t>Coquette Cutie Vibes: Quilted Cosmetic Bag with the Prettiest Bows With its dreamy quilted texture and dainty bow print, this cute makeup bag adds serious charm to your vanity, purse, or travel kit. It's soft, stylish, and just the right size to stash all your essentials (hello lip gloss, lash curler, and your fave perfume roller). Whether you're c</t>
+          <t>Add Some Flair to Your Sip with Our Bow Tumbler! Bow-tifully hydrated, anyone? Embrace the latest coquette trend with our new multi-colored tumbler . Featuring a vibrant, playful design, this bow tumbler is perfect for adding a girly touch to your day. You can enjoy the large 38 oz capacity that ensures you'll stay refreshed all day long. This tumb</t>
         </is>
       </c>
       <c r="G76" s="8" t="inlineStr"/>
@@ -3233,22 +3233,22 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>Brown Leopard Makeup Bag Travel</t>
+          <t>Multicolored Hearts Mint Tumbler Cup w/ Handle</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>makeup bags</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>Leopard</t>
+          <t>Mint Hearts</t>
         </is>
       </c>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>Wild About Glam— This Makeup Bag's a Vibe Get ready to glam like a queen with this bold leopard makeup bag! It's soft, quilted, and made to keep your beauty routine looking as wild as you are. From foundation to falsies, this cute makeup bag holds all the essentials‚ and looks so good doing it. Whether you're jetting off for a weekend or just organ</t>
+          <t>Valentine's Day ready with an adorable mint tumbler with colorful hearts all over it! Tell your boyfriend to get this for you for Valentine's Day. Or equip your Galentine's Day with this one. Whichever you choose, they're going to love it. 38 ounces includes reusable plastic straw all-day chill or heat stainless steel interior dishwasher safe screw</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr"/>
@@ -3268,22 +3268,22 @@
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>Black Metallic Sling Bag Women</t>
+          <t>Music Girl Icons Drink Tumbler</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>sling bags</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>Black Metallic</t>
+          <t>Light Pink Music Girl</t>
         </is>
       </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>Black Metallic Sling Bag = Instant Outfit Upgrade Say goodbye to boring bags and hello to shimmer on the go. This metallic sling bag is your new favorite plus-one, whether you're running errands, grabbing coffee, or snapping selfies. The black metallic finish is bold but wearable, and the comfy strap lets you throw it on and get moving (hands-free,</t>
+          <t>Shake it off and stay hydrated with Mimmolo's new stainless steel tumbler! Whether you're chasing your wildest dreams or looking to be hydrated all to well, this music icon stainless steel tumbler is everything. Featuring iconic references from chart-topping hits, this travel tumbler cup is your perfect match for sipping all day. Whether you're dan</t>
         </is>
       </c>
       <c r="G78" s="8" t="inlineStr"/>
@@ -3303,22 +3303,22 @@
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>Black Quilted Crossbody Sling Bag</t>
+          <t>Navy Daisy Tumbler Cup with Handle</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>sling bags</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Navy Daisy</t>
         </is>
       </c>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>We all know quilted tote bags are trending (see our array of colors!) but have you seen quilted sling bags!? Introducing the Black Quilted Crossbody Sling Bag - your classic sling bag but with quilted fabric all over it. Bound to sell out - QUICK! 13.5" x 7.2" x 3.6" 100% polyester large zipper closure Interior pocket within zipper closure adjustab</t>
+          <t>Add a little sunshine to your days with the Groovy Daisy Tumbler from Mimmolo! Want to get away from those ordinary tumblers? The Groovy Daisy Tumbler brings a pop of color and fun to any day. This 40-ounce navy tumbler, complete with an easy-to-hold handle, is made for on-the-go sipping. Featuring colorful florals and comes with its own drinking s</t>
         </is>
       </c>
       <c r="G79" s="8" t="inlineStr"/>
@@ -3338,22 +3338,22 @@
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>Silver Metallic Women's Sling Bag</t>
+          <t>Pickleball Social Club 38 Oz Tumbler with Lid Handle</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>sling bags</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>Silver Metallic</t>
+          <t>Preppy Light Pink and Green</t>
         </is>
       </c>
       <c r="F80" s="8" t="inlineStr">
         <is>
-          <t>Sling It On: Silver Metallic Sling Bag Cue the compliments, our Silver Metallic Sling Bag is that girl. With its metallic silver finish, black hardware, and quilted detailing, this crossbody bag is the ultimate upgrade to any OOTD. Toss it on for coffee runs, date nights, or your next travel day‚ the kind of bag that makes your fit feel put togethe</t>
+          <t xml:space="preserve">Ready to serve up style and stay hydrated? Ace your hydration game with the new Mimmolo Pickleball Social Club 38 Oz Tumbler with Lid &amp; Handle. This stainless steel tumbler is here to keep your drinks chill during every pickleball game and beyond! With a secure lid to keep spills in check and a handle for easy carry, this tumbler fits perfectly in </t>
         </is>
       </c>
       <c r="G80" s="8" t="inlineStr"/>
@@ -3373,22 +3373,22 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>Black Bow Print Puffer Tote</t>
+          <t>Pink Purple Green Swirl Tumbler Cup</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>tote bags</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>Black and White Bows</t>
+          <t>Light Pink and Purple Swirl</t>
         </is>
       </c>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>Bow Down to the Ultimate Quilted Tote Bag Your everyday errands just got an upgrade with this Black Bow Mini Puffer Tote. Between the puffed quilting and sweet bow accents, it's the ultimate accessory for any outfit that needs a little girly flair. Small enough to stay light, roomy enough to carry your phone, gloss, and wallet‚ it's everything. Whe</t>
+          <t>Swirls are so in. This pink, purple and green mix is the perfect fall touch to a good 38 oz tumbler. Each tumbler by Mimmolo comes with a matching lid and straw. Perfect as a gift, or for yourself! 38 ounces includes reusable plastic straw all-day chill or heat stainless steel interior dishwasher safe screw-on plastic top with straw opening adjusta</t>
         </is>
       </c>
       <c r="G81" s="8" t="inlineStr"/>
@@ -3408,22 +3408,22 @@
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>Black X-Large Quilted Tote</t>
+          <t>Pink Santas 38 Oz Tumbler</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>tote bags</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Light Pink Santa</t>
         </is>
       </c>
       <c r="F82" s="8" t="inlineStr">
         <is>
-          <t>20" x 7" x 15" zipper closure 27" long strap water-resistant inner lining two interior pockets two exterior side pockets</t>
+          <t>Sleigh All Day with This Pink Santa Tumbler Cup Calling all holiday lovers— this Pink Santa Tumbler Cup is pure Christmas cheer! Whether you're sipping hot cocoa while wrapping gifts or iced coffee on the go, this stainless steel tumbler keeps your drinks at the perfect temp. The pink Santa print adds just the right touch of girly holiday magic. Wi</t>
         </is>
       </c>
       <c r="G82" s="8" t="inlineStr"/>
@@ -3443,22 +3443,22 @@
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>Black and White Polka Dot Mini Puffer Tote</t>
+          <t>Pink and Hot Pink Striped Drink Tumbler</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>tote bags</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>Black and White Polka Dots</t>
+          <t>Pink and Hot Pink</t>
         </is>
       </c>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>Spotted in Style: Black &amp; White Mini Tote This Black and White Polka Dot Mini Tote is your new go-to for playful meets practical. With its puffer quilting and trendy spotted design, it's cute enough to grab compliments and cozy enough for everyday carry. It's small, but mighty in style points. Perfect for brunch, errands, or a cozy coffee shop hang</t>
+          <t>Everyday Essential: 38 oz Pink Striped Tumbler Cup Meet the tumbler that’s about to take center stage in your daily routine. Our 38 oz pink striped tumbler cup is not just a cup, it’s a statement piece for your desk, car, or poolside setup. With its playful pink-on-pink vertical stripes, it’s chic enough to match your vibe while being practical eno</t>
         </is>
       </c>
       <c r="G83" s="8" t="inlineStr"/>
@@ -3478,22 +3478,22 @@
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>Brown Leopard Mini Puffer Tote Bag</t>
+          <t>Pink and Orange Striped 30 Oz Tumbler Cup</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>tote bags</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>Leopard</t>
+          <t>Pink and Orange</t>
         </is>
       </c>
       <c r="F84" s="8" t="inlineStr">
         <is>
-          <t>Spots and Style: The Leopard Mini Tote Bag You Need Channel your inner wild side with this Brown Leopard Mini Tote Bag. It's quilted, it's cute, and it gives off the perfect puffer texture for cooler weather outfits. The all-over leopard print makes it an eye-catcher, while the size keeps it light enough for daily use. Whether you're styling a coff</t>
+          <t>Sip Happy with Our Pink and Orange Striped Travel Tumbler Cup Some days call for more than basic black — they call for color. Meet the pink and orange striped tumbler cup, designed for anyone who wants hydration with a side of fun. This travel tumbler cup isn’t just a pretty face; it’s insulated, comes with a sturdy handle, and keeps your drinks pe</t>
         </is>
       </c>
       <c r="G84" s="8" t="inlineStr"/>
@@ -3513,22 +3513,22 @@
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>Aqua and Green Striped Tumbler Pouches</t>
+          <t>Pink and Wine Striped 30 Oz Cabana Tumbler</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>tumbler pouches</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>Aqua and Green Stripe</t>
+          <t>Pink and Wine</t>
         </is>
       </c>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>The Striped Tumbler Pouch Makes Hydration Look Fun If you’ve ever wanted your tumbler to look like it just stepped off a beach vacation without you, this Aqua and Green Striped Tumbler Pouch is here to make that dream a reality. With breezy coastal colors and playful summer stripes, this Tumbler Zipper Bag gives your cup serious “I belong on a yach</t>
+          <t>Pink Striped Tumbler Cup for Cute Hydration Goals Because boring cups just won’t cut it anymore. Our pink striped tumbler cup is here to upgrade your hydration game with major cuteness and practicality. Designed with candy-colored stripes, this travel tumbler cup is double-walled, insulated, and complete with a sturdy handle for easy carrying. Perf</t>
         </is>
       </c>
       <c r="G85" s="8" t="inlineStr"/>
@@ -3548,22 +3548,22 @@
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>Baseball Happy Face Tumbler ZIPPER POUCH</t>
+          <t>Plum Tumbler Cup w/ Handle</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>tumbler pouches</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>White Baseball Happy Face</t>
+          <t>Plum</t>
         </is>
       </c>
       <c r="F86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unleash the fun and functionality with our Baseball Happy Face Tumbler Zipper Pouch! But what exactly is a Zipper Pouch? Think of it as a stylish sidekick for your tumbler - a compact pouch that not only adds a touch of flair with baseball smiley faces but also serves as a practical storage solution. A Zipper Pouch is a mini bag designed to attach </t>
+          <t>Finally! A plum purple tumbler cup that will retain ice overnight. This 40 oz tumbler cup comes with a handle, a plastic straw and a matching lid. More solid colors to love! 40 ounces includes reusable plastic straw all-day chill or heat stainless steel interior dishwasher safe screw-on plastic top with straw opening adjustable straw cover for easy</t>
         </is>
       </c>
       <c r="G86" s="8" t="inlineStr"/>
@@ -3583,22 +3583,22 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>Beach Seashells Tumbler Sling Bag</t>
+          <t>Queen of the Green Golf 38 Oz Tumbler with Lid Handle</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>tumbler pouches</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>Light Pink</t>
+          <t>Golf Green</t>
         </is>
       </c>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>The Seashell Pouch That Turns Every Sip Into a Vacation If your inner mermaid has been patiently waiting for an accessory worthy of her beach-loving heart, she can finally relax, the Beach Seashells Tumbler Zipper Bag has arrived. Featuring adorable seashells, coral shapes, and sunshine-approved colors, this Tumbler Pouch basically screams, “Take m</t>
+          <t>Swing into style with the Queen of the Green Golf 38 Oz Tumbler! ⛳️ For all the golf lovers out there, this Queen of the Green Golf 38 Oz Tumbler is your new go-to for staying hydrated while you slay the course. With a sleek design, it features both a top lid and a side handle, making it easy to carry and sip between swings. The 38 oz capacity mean</t>
         </is>
       </c>
       <c r="G87" s="8" t="inlineStr"/>
@@ -3618,22 +3618,22 @@
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>Black &amp; Pink Mini Coquette Bows Tumbler ZIPPER POUCH</t>
+          <t>Replacement Tumbler Lids</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>tumbler pouches</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>Black and Pink Bows</t>
+          <t>Orchid, White, Mint, Light Blue, Hot Pink</t>
         </is>
       </c>
       <c r="F88" s="8" t="inlineStr">
         <is>
-          <t>Picture a lovely light pink canvas adorned with a delightful pattern of mini black bows, creating a charming and playful visual appeal. The Black &amp; Pink Mini Coquette Bows add a touch of elegance to this pouch, making it a perfect accessory for those who appreciate the finer details in their daily essentials. This ZIPPER POUCH is not just about loo</t>
+          <t xml:space="preserve">Are you a chic girl looking for the perfect replacement lid to go with your 40 oz tumbler cup? Look no further, because you've just found it! Mimmolo has the perfect Tumbler Lid Replacement for you that will instantly transform your old and average cup into something amazing. Accidents happen, but now they're not such a problem! Let it be dropping </t>
         </is>
       </c>
       <c r="G88" s="8" t="inlineStr"/>
@@ -3653,22 +3653,22 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>Black &amp; White Bows Tumbler Pouch</t>
+          <t>Ridged Tumbler Lid Replacements</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>tumbler pouches</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>White, Pink, Light Blue, Mint, Light Pink</t>
         </is>
       </c>
       <c r="F89" s="8" t="inlineStr">
         <is>
-          <t>Your New Everyday Bow-Obsessed Tumbler Zipper Bag Meet the Black &amp; White Bows Tumbler Pouch, the girly little sidekick your tumbler has been manifesting. If you believe bows make everything better (spoiler: they do), this adorable Tumbler Zipper Bag is about to become your new personality trait. Wrapped in the prettiest black-and-white bow pattern,</t>
+          <t>Screw-in top Lid fits on our 40 oz tumblers and 38 oz tumblers Try our top handle jug lids or our classic clear lids !</t>
         </is>
       </c>
       <c r="G89" s="8" t="inlineStr"/>
@@ -3688,22 +3688,22 @@
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>Black Water Bottle Zipper Pouch</t>
+          <t>Rose Pink Drink Tumbler Cup w/ Handle</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>tumbler pouches</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Rose Pink</t>
         </is>
       </c>
       <c r="F90" s="8" t="inlineStr">
         <is>
-          <t>Elevate your on-the-go experience with our Black Water Bottle Zipper Pouch, the perfect companion for your tumbler cup. Designed with practicality and style in mind, this versatile pouch attaches effortlessly to your tumbler with an adjustable velcro strap. Whether you're heading out for a walk, hitting the gym, or running errands, this pouch keeps</t>
+          <t xml:space="preserve">We love a pink pink pink girl. And now we have another shade of pink to add to our solid tumblers inventory! This soft rose pink tumbler holds 40 ounces of water, retains heat or cold overnight, and has a handle to easily hold. 40 ounces includes reusable plastic straw all-day chill or heat stainless steel interior dishwasher safe screw-on plastic </t>
         </is>
       </c>
       <c r="G90" s="8" t="inlineStr"/>
@@ -3723,22 +3723,22 @@
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>Brown Leopard Tumbler Sling Bag</t>
+          <t>Santa Claus Repeat Holiday Tumbler Cup</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>tumbler pouches</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Pink and Red Santa</t>
         </is>
       </c>
       <c r="F91" s="8" t="inlineStr">
         <is>
-          <t>Your Wildly Cute Leopard Tumbler Pouch Is Calling This Brown Leopard Tumbler Pouch is fierce, fun, and guaranteed to get compliments from strangers who “just have to know where you got that.” Mimmolo's newest Tumbler Zipper Bag takes your everyday tumbler and turns it into a full outfit accessory. Like jewelry. But for hydration. The adjustable vel</t>
+          <t>Make your holiday season extra jolly with the Santa Claus Repeat Holiday Tumbler Cup from Mimmolo.com. This adorable pink tumbler is adorned with an abundance of cheerful Santa Claus designs, bringing a festive and whimsical touch to your drinkware collection. With its convenient handle and included straw, this tumbler is perfect for young women wh</t>
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr"/>
@@ -3758,22 +3758,22 @@
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>Brown and White Cow Print Tumbler ZIPPER POUCH</t>
+          <t>Skull Flower Bow Drink Tumbler</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>tumbler pouches</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>Brown and White Cow</t>
+          <t>Light Pink Skull Flowers</t>
         </is>
       </c>
       <c r="F92" s="8" t="inlineStr">
         <is>
-          <t>Saddle up your tumbler with the Brown and White Cow Print Tumbler Zipper Pouch - the hottest accessory for all the cowgirls out there! This isn't just a Zipper Pouch; it's a stylish fanny pack for your tumbler, adding a touch of western flair to your daily routine. Designed with the iconic brown and white cow print, this Zipper Pouch is both functi</t>
+          <t>Gen Z is going to love this. Skulls. Flowers. Coquette bows. We're mixing all things trending for the young demographic. Plus it's perfect around Halloween. We all had our emo girl era... right? 38 ounces includes reusable plastic straw all-day chill or heat stainless steel interior dishwasher safe screw-on plastic top with straw opening adjustable</t>
         </is>
       </c>
       <c r="G92" s="8" t="inlineStr"/>
@@ -3793,22 +3793,22 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>Cherry Bow Tumbler Pouches</t>
+          <t>Softball Happy Face 40 Oz Tumbler</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>tumbler pouches</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>Light Pink Cherry Bows</t>
+          <t>White Softball</t>
         </is>
       </c>
       <c r="F93" s="8" t="inlineStr">
         <is>
-          <t>Keep your essentials cute and close with the Cherry Bow Tumbler Zipper Pouch! This adorable zipper pouch is your new hands-free must-have, perfect for storing your small items while adding a pop of personality to your day. With its playful cherry bow design, it's the cutest accessory you'll never want to leave home without. Want to make it a set? P</t>
+          <t>Hit a home run with the Softball Happy Face 40 Oz Tumbler! This large stainless steel tumbler is all about bringing the good vibes and staying hydrated, whether you're on the field or chilling off the clock. Featuring an adorable smiley face and bold design, this tumbler is your new best friend for every game day and beyond. With a massive 40 oz ca</t>
         </is>
       </c>
       <c r="G93" s="8" t="inlineStr"/>
@@ -3828,22 +3828,22 @@
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>Chinoiserie Coquette Bows Tumbler Zipper Pouch</t>
+          <t>Spring Flowers Tumbler with Handle</t>
         </is>
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>tumbler pouches</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>Light Blue Bows</t>
+          <t>Multicolored Spring Florals</t>
         </is>
       </c>
       <c r="F94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Say hello to your new favorite accessory! The Chinoiserie Coquette Bows Tumbler Zipper Pouch is the trendy, hands-free solution you've been waiting for. Featuring a cute toile print with playful coquette bows, this pouch is perfect for storing your essentials while keeping your hands free for all the fun. Whether you're grabbing coffee or just out </t>
+          <t>This tumbler is bringing all the spring feels with its vibrant floral design, perfect for sipping your iced coffee, smoothies, or water in style. Whether you’re soaking up the sunshine at the park or just need a cute, practical accessory for your everyday life, this 38 oz tumbler has you covered. With a handy side handle and a fit that slides right</t>
         </is>
       </c>
       <c r="G94" s="8" t="inlineStr"/>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>Cow Print Tumbler Water Bottle Zipper Pouch</t>
+          <t>Subtle Strawberry 38 Oz Tumbler Cup</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>tumbler pouches</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>Black and White Cow</t>
+          <t>Pink Strawberry</t>
         </is>
       </c>
       <c r="F95" s="8" t="inlineStr">
         <is>
-          <t>Add a touch of playful charm to your tumbler with our Cow Print Tumbler Water Bottle Zipper Pouch. This stylish accessory is designed to effortlessly attach to your tumbler cup, making it the perfect companion for your walks and outings. With its adjustable velcro strap, you can securely fasten this pouch and keep your essentials close at hand. The</t>
+          <t xml:space="preserve">Here’s a tumbler that’s berry cute and ready to be your hydration sidekick all day! The Subtle Strawberry 38 Oz Tumbler brings a fresh, understated strawberry pattern for those who love a hint of sweetness with their style. This travel tumbler cup has a sturdy handle for easy carry, fits perfectly in any car cup holder (road trip, anyone?), and is </t>
         </is>
       </c>
       <c r="G95" s="8" t="inlineStr"/>
@@ -3898,22 +3898,22 @@
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>Cowboy Happy Face Tumbler Fanny Pack</t>
+          <t>Sweet Orange Cup Tumbler</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>tumbler pouches</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>White Cowboy Happy Face</t>
+          <t>Light Pink</t>
         </is>
       </c>
       <c r="F96" s="8" t="inlineStr">
         <is>
-          <t>Saddle up and embrace the cheerful charm of our Cowboy Happy Face Tumbler Fanny Pack. This delightful accessory is designed to bring a smile to your face while keeping your essentials secure and easily accessible. With its adjustable velcro strap, this tumbler fanny pack attaches effortlessly to your favorite tumbler, creating the perfect companion</t>
+          <t>Fresh Orange Print Tumbler for Summer Days If summer had a signature cup, it would be the Sweet Orange Tumbler with Straw. Designed for the girl who loves bright colors, fun prints, and a little sunshine in her everyday routine, this tumbler brings citrus style to all your favorite moments. Whether you’re packing your beach bag, grabbing your morni</t>
         </is>
       </c>
       <c r="G96" s="8" t="inlineStr"/>
@@ -3933,22 +3933,22 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>Dainty Florals Pink Tumbler Pouch Bag</t>
+          <t>Tennis Social Club 38 Oz Tumbler with Lid Handle</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>tumbler pouches</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>Light Pink and Blue Flowers</t>
+          <t>Light Pink Tennis</t>
         </is>
       </c>
       <c r="F97" s="8" t="inlineStr">
         <is>
-          <t>Your Tumbler's New Bestie: The Dainty Florals Pink Tumbler Zipper Pouch! Ready to keep your essentials cute and organized? This tumber fanny pack is here to step up your accessory game. This chic pouch fits perfectly around your tumbler, making it the ultimate combo of style and function. It's perfect for holding your small must-haves—think keys, l</t>
+          <t>Whether you're serving aces on the court or just need a cool way to stay hydrated, this Mimmolo Tennis Social Club tumbler is your perfect match! With a top lid handle and side handle, it’s super easy to grab and go, and the 38 oz size means you can sip on your favorite drink all day long. Plus, it fits perfectly in your cup holder, so you can keep</t>
         </is>
       </c>
       <c r="G97" s="8" t="inlineStr"/>
@@ -3968,22 +3968,22 @@
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>Fall Leaves Tumbler Zipper Pouch</t>
+          <t>Tumbler Cup 38 Oz Jug (Yellow and Aqua Striped)</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>tumbler pouches</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>Multicolored Fall Leaves</t>
+          <t>Yellow and Aqua</t>
         </is>
       </c>
       <c r="F98" s="8" t="inlineStr">
         <is>
-          <t>This zipper pouch has a multicolored fall leaves design all over it. This neoprene pouch has pockets inside and out to carry your phone, cards and keys on your walk! “Your tumbler’s new favorite belt bag!” 7” x 4.75” neoprene material large zipper pocket 2 exterior pockets (one netted) for cards or phone adjustable velcro strap to go around tumbler</t>
+          <t>Cutest Travel Tumbler Cup with Built-In Straw + Dual Handles Ready to meet the tumbler of your dreams? Our yellow and aqua striped 38 oz tumbler cup is designed to make hydration not just easier but way more fun. With its vibrant two-toned stripes in a trendy yellow and blue and oversized capacity, this cute tumbler cup is ready for iced lattes, wa</t>
         </is>
       </c>
       <c r="G98" s="8" t="inlineStr"/>
@@ -4003,22 +4003,22 @@
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>Flower Power Tumbler Zipper Caddy</t>
+          <t>Whimsical Roses Tumbler with Straw</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>tumbler pouches</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>Peach and Red</t>
+          <t>Light Pink</t>
         </is>
       </c>
       <c r="F99" s="8" t="inlineStr">
         <is>
-          <t>Add a touch of floral charm to your tumbler experience with our Flower Power Tumbler Zipper Caddy. This versatile accessory, also known as a tumbler fanny pack or belt bag, is designed to effortlessly attach to your tumbler cup using an adjustable velcro strap. Now you can enjoy your walks or outdoor adventures while keeping your essentials like ph</t>
+          <t xml:space="preserve">Your New Favorite Floral Tumbler with Straw The Whimsical Roses Tumbler Cup brings joyful, garden-inspired energy to every part of your day. Designed for anyone who loves florals, fun, and accessories that feel instantly uplifting, this tumbler with straw turns something as simple as staying hydrated into a bright, stylish moment. If you like your </t>
         </is>
       </c>
       <c r="G99" s="8" t="inlineStr"/>
@@ -4038,22 +4038,22 @@
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>Groovy Multicolored Flowers Tumbler Zipper Pouch</t>
+          <t>XO Cherries Valentine's Day Tumbler with Lid Handle</t>
         </is>
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>tumbler pouches</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>Light Pink</t>
+          <t>Mint XO Cherries</t>
         </is>
       </c>
       <c r="F100" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Tumbler Pouch That Turns Every Day Into a Spring Mood If sunshine, nostalgia, and your favorite colorful sundress magically turned into an accessory, it would be this Groovy Multicolored Flowers Tumbler Pouch. Covered in retro-inspired blossoms, this Tumbler Zipper Bag is basically the embodiment of “good vibes only”, and yes, it will absolutely </t>
+          <t>Love You Cherry Much: Your Cutest Tumbler Yet Sippin' sweet never looked so cute! This XO Cherries Stainless Steel Tumbler is your go-to for flirty hydration. Covered in cherry and kiss motifs, it adds a playful touch to your daily coffee or matcha moment. With a sturdy lid and comfy handle, this tumbler cup is ready for everything from early morni</t>
         </is>
       </c>
       <c r="G100" s="8" t="inlineStr"/>
@@ -4073,22 +4073,22 @@
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>Hot Pink Tumbler Fanny Pack</t>
+          <t>Yellow and Aqua Striped 30 Oz Tumbler Cup</t>
         </is>
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>tumbler pouches</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>Hot Pink</t>
+          <t>Yellow and Aqua</t>
         </is>
       </c>
       <c r="F101" s="8" t="inlineStr">
         <is>
-          <t>Introducing our Hot Pink Tumbler Fanny Pack, the ultimate accessory for women who value convenience and style. This innovative pouch attaches securely to your tumbler cup using an adjustable Velcro strap, allowing you to carry your essentials effortlessly while on the go. Whether you're out for a leisurely walk, running errands, or exploring new de</t>
+          <t>Bold &amp; Bright Striped Tumbler Cup for Everyday Hydration Hydration, but make it cute. Our striped tumbler cup in yellow and aqua blue is the perfect mix of trendy design and practical function. With playful pastel stripes and a sturdy handle, this travel tumbler cup keeps your drinks cold for hours (or hot if that’s your vibe). Lightweight yet dura</t>
         </is>
       </c>
       <c r="G101" s="8" t="inlineStr"/>
@@ -4108,22 +4108,22 @@
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>Italian Summer Tumbler Belt Bag</t>
+          <t>Zesty Lemons Drink Tumbler</t>
         </is>
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>tumbler pouches</t>
+          <t>tumblers</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>Mint</t>
+          <t>Light Blue</t>
         </is>
       </c>
       <c r="F102" s="8" t="inlineStr">
         <is>
-          <t>Your Passport to La Dolce Vita: The Italian Summer Tumbler Zipper Bag Say “ciao” to your new warm-weather obsession! The Italian Summer Tumbler Sling Bag is the accessory that lets you pretend you’re wandering Capri even if you’re actually power-walking around the block. This charming Tumbler Pouch is covered in sun-drenched motifs inspired by mark</t>
+          <t>Refresh Your Routine with the Zesty Lemons Tumbler If your drinkware could capture the feeling of a perfect summer afternoon, it would look exactly like the Zesty Lemons Tumbler Cup. This stainless steel reusable tumbler is made for the girl who loves warm weather, colorful accessories, and anything that brings a little joy to her daily routine. Wi</t>
         </is>
       </c>
       <c r="G102" s="8" t="inlineStr"/>
@@ -4143,22 +4143,22 @@
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>Light Blue Tumbler Backpack Zipper Pouch</t>
+          <t>Black &amp; Pink Mini Bows Wine Tumbler Cup</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>tumbler pouches</t>
+          <t>wine tumblers</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>Light Blue</t>
+          <t>Light Pink</t>
         </is>
       </c>
       <c r="F103" s="8" t="inlineStr">
         <is>
-          <t>Introducing our Light Blue Tumbler Backpack Zipper Pouch, the perfect accessory for women who value both convenience and style. This innovative pouch attaches securely to your tumbler cup via an adjustable Velcro strap, creating a hands-free solution to carry your essentials during walks, hikes, or any on-the-go adventure. With its one large zipper</t>
+          <t xml:space="preserve">Sip Cute With This Bow Moment If you love anything covered in bows, this Black &amp; Pink Mini Bows 12 Oz Wine Tumbler is about to be your new daily sidekick. The soft pink background and tiny black bows give it that sweet, girly vibe you can’t help but show off, and the stainless steel interior keeps every sip the perfect temperature. As an insulated </t>
         </is>
       </c>
       <c r="G103" s="8" t="inlineStr"/>
@@ -4178,22 +4178,22 @@
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>Light Blue and Navy Striped Velcro Bag for Tumbler</t>
+          <t>Cow Print Wine Tumbler Cup With Lid</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>tumbler pouches</t>
+          <t>wine tumblers</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>Light Blue and Navy</t>
+          <t>White</t>
         </is>
       </c>
       <c r="F104" s="8" t="inlineStr">
         <is>
-          <t>The Coastal-Cutie Tumbler Pouch Your Summer Needs If “nautical chic but make it adorable” were a thing (it is now), it would 100% be this Light Blue and Navy Striped Tumbler Pouch. This Tumbler Zipper Bag turns your everyday tumbler into a preppy little accessory that screams beach day, boat day, pool day, farmers market day. Inside, you’ve got a s</t>
+          <t xml:space="preserve">The Tumbler That Makes Every Sip More Fun Your drinkware lineup just got a whole lot cuter with this Cow Printed 12 Oz Wine Tumbler. If you love a fun western moment or just appreciate a bold print, this insulated wine tumbler is ready to go wherever you do. The stainless steel build keeps every sip cold longer, and the cow print turns an everyday </t>
         </is>
       </c>
       <c r="G104" s="8" t="inlineStr"/>
@@ -4213,22 +4213,22 @@
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>Light Pink Tumbler Bottle Zipper Pouch</t>
+          <t>Dainty Florals Pink WINE TUMBLER Cup</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>tumbler pouches</t>
+          <t>wine tumblers</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>Light Pink</t>
+          <t>Light Pink and Blue Flowers</t>
         </is>
       </c>
       <c r="F105" s="8" t="inlineStr">
         <is>
-          <t>Introducing our Light Pink Tumbler Zipper Pouch, the perfect companion for women who want to combine style and convenience in their daily adventures. This versatile pouch attaches seamlessly to your tumbler cup with an adjustable Velcro strap, transforming it into a fashionable and functional accessory. With its one large zipper pocket and exterior</t>
+          <t>The Dainty Florals Pink Wine Tumbler is here to bring major soft girl vibes to your drink game. Featuring a delicate floral print on a pastel pink backdrop, this stemless tumbler is perfect for sipping in style—whether it's wine o'clock or matcha time. Double-wall insulation : Keeps drinks cold for hours or your coffee hot Portable &amp; chic : Perfect</t>
         </is>
       </c>
       <c r="G105" s="8" t="inlineStr"/>
@@ -4248,22 +4248,22 @@
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>Lobsters Bag for Tumbler</t>
+          <t>Lucky Girl Western Insulated Wine Tumbler</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>tumbler pouches</t>
+          <t>wine tumblers</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>Pink</t>
+          <t>Lucky Mint</t>
         </is>
       </c>
       <c r="F106" s="8" t="inlineStr">
         <is>
-          <t>Your New Tumbler Sidekick: The Cutest Tumbler Zipper Bag Ever Meet the Lobster Tumbler Belt Bag, the only accessory that says, “Yes, I hydrate and yes, I do it with flair.” This adorable Tumbler Pouch comes decked out in bright, beachy lobster vibes that instantly transport you to seaside strolls, clam-bake nights, and summer days where your only r</t>
+          <t>Sippin' in style just got a wild upgrade with the Lucky Girl Western Insulated Wine Tumbler ! This stemless tumbler is serving major western vibes with its fun, on-trend doodles and a poppin' design that’s cute and cowgirl chic . Whether you're sipping wine, iced tea, or a spicy margarita, this stemless wine tumbler keeps your drinks at the perfect</t>
         </is>
       </c>
       <c r="G106" s="8" t="inlineStr"/>
@@ -4283,22 +4283,22 @@
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>Multicolored Coquette Bows Tumbler Zipper Pouch</t>
+          <t>Toile Coquette Bows WINE TUMBLER Cup</t>
         </is>
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>tumbler pouches</t>
+          <t>wine tumblers</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>Multicolored Bows</t>
+          <t>Light Blue Bows</t>
         </is>
       </c>
       <c r="F107" s="8" t="inlineStr">
         <is>
-          <t>Introducing the Multicolored Coquette Bows Tumbler ZIPPER POUCH - the latest trendsetter in the world of accessories! Elevate your style with this adjustable bag designed to effortlessly attach to your tumbler, providing a chic solution for carrying your essentials on the go. This trendy ZIPPER POUCH boasts a sleek white background adorned with a d</t>
+          <t>Sip in style with the Chinoiserie Coquette Bows Wine Tumbler ! This stemless tumbler is serving elegant meets flirty vibes with its chic toile-inspired print and dainty bow accents. Whether you’re toasting with your favorite wine, keeping your coffee hot, or indulging in a cozy tea moment, this tumbler has your back (and your drink). Double-wall in</t>
         </is>
       </c>
       <c r="G107" s="8" t="inlineStr"/>
@@ -4307,2736 +4307,6 @@
       <c r="J107" s="8" t="inlineStr"/>
       <c r="K107" s="8" t="inlineStr"/>
     </row>
-    <row r="108">
-      <c r="A108" s="6" t="n">
-        <v>107</v>
-      </c>
-      <c r="B108" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C108" s="8" t="inlineStr">
-        <is>
-          <t>Multicolored Maroon Floral Tumbler Zipper Pouch</t>
-        </is>
-      </c>
-      <c r="D108" s="8" t="inlineStr">
-        <is>
-          <t>tumbler pouches</t>
-        </is>
-      </c>
-      <c r="E108" s="8" t="inlineStr">
-        <is>
-          <t>Maroon Floral</t>
-        </is>
-      </c>
-      <c r="F108" s="8" t="inlineStr">
-        <is>
-          <t>Comes in a matching tumbler! This sell-out style is perfect for fall. A cute maroon tumbler with flowers all over it. This will have your friends saying "okay now that is cute." “Your tumbler’s new favorite belt bag!” 7” x 4.75” neoprene material large zipper pocket 2 exterior pockets (one netted) for cards or phone adjustable velcro strap to go ar</t>
-        </is>
-      </c>
-      <c r="G108" s="8" t="inlineStr"/>
-      <c r="H108" s="8" t="inlineStr"/>
-      <c r="I108" s="8" t="inlineStr"/>
-      <c r="J108" s="8" t="inlineStr"/>
-      <c r="K108" s="8" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="6" t="n">
-        <v>108</v>
-      </c>
-      <c r="B109" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C109" s="8" t="inlineStr">
-        <is>
-          <t>Pastel Happy Face Zipper Pouch for Tumbler</t>
-        </is>
-      </c>
-      <c r="D109" s="8" t="inlineStr">
-        <is>
-          <t>tumbler pouches</t>
-        </is>
-      </c>
-      <c r="E109" s="8" t="inlineStr">
-        <is>
-          <t>Pastel</t>
-        </is>
-      </c>
-      <c r="F109" s="8" t="inlineStr">
-        <is>
-          <t>Add a touch of convenience and style to your tumbler experience with our Pastel Happy Face Zipper Pouch for Tumbler. This versatile accessory, also known as a tumbler fanny pack or belt bag, is designed to attach seamlessly to your tumbler cup, keeping your essentials like phone, wallet, and keys close at hand during walks or outings. Embrace the w</t>
-        </is>
-      </c>
-      <c r="G109" s="8" t="inlineStr"/>
-      <c r="H109" s="8" t="inlineStr"/>
-      <c r="I109" s="8" t="inlineStr"/>
-      <c r="J109" s="8" t="inlineStr"/>
-      <c r="K109" s="8" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="6" t="n">
-        <v>109</v>
-      </c>
-      <c r="B110" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C110" s="8" t="inlineStr">
-        <is>
-          <t>Pink Purple Green Swirl Tumbler Zipper Pouch</t>
-        </is>
-      </c>
-      <c r="D110" s="8" t="inlineStr">
-        <is>
-          <t>tumbler pouches</t>
-        </is>
-      </c>
-      <c r="E110" s="8" t="inlineStr">
-        <is>
-          <t>Light Pink and Purple Swirl</t>
-        </is>
-      </c>
-      <c r="F110" s="8" t="inlineStr">
-        <is>
-          <t>Tumbler zipper pouches have a velcro attachment to carry your phone, wallet and keys on that hot girl walk. No need for a purse with the cutest Pink Purple Green Swirl Tumbler Zipper Pouch! “Your tumbler’s new favorite belt bag!” 7” x 4.75” neoprene material large zipper pocket 2 exterior pockets (one netted) for cards or phone adjustable velcro st</t>
-        </is>
-      </c>
-      <c r="G110" s="8" t="inlineStr"/>
-      <c r="H110" s="8" t="inlineStr"/>
-      <c r="I110" s="8" t="inlineStr"/>
-      <c r="J110" s="8" t="inlineStr"/>
-      <c r="K110" s="8" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="6" t="n">
-        <v>110</v>
-      </c>
-      <c r="B111" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C111" s="8" t="inlineStr">
-        <is>
-          <t>Pink and Hot Pink Striped Tumbler Pouch Bag</t>
-        </is>
-      </c>
-      <c r="D111" s="8" t="inlineStr">
-        <is>
-          <t>tumbler pouches</t>
-        </is>
-      </c>
-      <c r="E111" s="8" t="inlineStr">
-        <is>
-          <t>Pink and Hot Pink</t>
-        </is>
-      </c>
-      <c r="F111" s="8" t="inlineStr">
-        <is>
-          <t>The Striped Tumbler Zipper Bag That Does The Most There are cute accessories… and then there’s this Pink &amp; Hot Pink Striped Tumbler Pouch. This Tumbler Zipper Bag is for the girl who loves pink, needs her essentials within reach, and refuses to apologize for having fabulous taste. The hot-pink stripes bring the drama (the fun kind), while the light</t>
-        </is>
-      </c>
-      <c r="G111" s="8" t="inlineStr"/>
-      <c r="H111" s="8" t="inlineStr"/>
-      <c r="I111" s="8" t="inlineStr"/>
-      <c r="J111" s="8" t="inlineStr"/>
-      <c r="K111" s="8" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="6" t="n">
-        <v>111</v>
-      </c>
-      <c r="B112" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C112" s="8" t="inlineStr">
-        <is>
-          <t>Pink and Orange Striped Tumbler Pouch</t>
-        </is>
-      </c>
-      <c r="D112" s="8" t="inlineStr">
-        <is>
-          <t>tumbler pouches</t>
-        </is>
-      </c>
-      <c r="E112" s="8" t="inlineStr">
-        <is>
-          <t>Pink and Orange</t>
-        </is>
-      </c>
-      <c r="F112" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The Striped Tumbler Zipper Bag That Steals the Spotlight One glance and you’re instantly in your “she’s fun, she’s cute, she’s hydrated” era. This adorable Tumbler Zipper Bag is the ultimate sidekick for women who refuse to choose between being organized and being on-trend! Designed to strap right onto your matching tumbler (sold separately), this </t>
-        </is>
-      </c>
-      <c r="G112" s="8" t="inlineStr"/>
-      <c r="H112" s="8" t="inlineStr"/>
-      <c r="I112" s="8" t="inlineStr"/>
-      <c r="J112" s="8" t="inlineStr"/>
-      <c r="K112" s="8" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="6" t="n">
-        <v>112</v>
-      </c>
-      <c r="B113" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C113" s="8" t="inlineStr">
-        <is>
-          <t>Pink and Wine Striped Velcro Bag for Tumbler</t>
-        </is>
-      </c>
-      <c r="D113" s="8" t="inlineStr">
-        <is>
-          <t>tumbler pouches</t>
-        </is>
-      </c>
-      <c r="E113" s="8" t="inlineStr">
-        <is>
-          <t>Pink and Wine</t>
-        </is>
-      </c>
-      <c r="F113" s="8" t="inlineStr">
-        <is>
-          <t>Your Cup Called — She Wants This Tumbler Zipper Bag Prepare to fall head over heels for the Pink &amp; Wine Striped Tumbler Pouch Bag, the accessory that proves your tumbler deserves to dress up too. This flirty little Tumbler Zipper Bag is the perfect blend of “I’m organized” and “I’m adorable,” giving your daily hydration routine a much-needed glow-u</t>
-        </is>
-      </c>
-      <c r="G113" s="8" t="inlineStr"/>
-      <c r="H113" s="8" t="inlineStr"/>
-      <c r="I113" s="8" t="inlineStr"/>
-      <c r="J113" s="8" t="inlineStr"/>
-      <c r="K113" s="8" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="6" t="n">
-        <v>113</v>
-      </c>
-      <c r="B114" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C114" s="8" t="inlineStr">
-        <is>
-          <t>Red Flower Happy Face Tumbler Zipper Pouch</t>
-        </is>
-      </c>
-      <c r="D114" s="8" t="inlineStr">
-        <is>
-          <t>tumbler pouches</t>
-        </is>
-      </c>
-      <c r="E114" s="8" t="inlineStr">
-        <is>
-          <t>Red Flower Happy Face</t>
-        </is>
-      </c>
-      <c r="F114" s="8" t="inlineStr">
-        <is>
-          <t>Introducing the Red Flower Happy Face Tumbler Zipper Pouch - the perfect fusion of style and functionality! This trendy accessory is tailor-made to accompany your favorite tumbler, offering a chic solution to keep your essentials close at hand. The hot pink backdrop adorned with vibrant red flowers and cheerful smiley faces creates a playful and ey</t>
-        </is>
-      </c>
-      <c r="G114" s="8" t="inlineStr"/>
-      <c r="H114" s="8" t="inlineStr"/>
-      <c r="I114" s="8" t="inlineStr"/>
-      <c r="J114" s="8" t="inlineStr"/>
-      <c r="K114" s="8" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="6" t="n">
-        <v>114</v>
-      </c>
-      <c r="B115" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C115" s="8" t="inlineStr">
-        <is>
-          <t>Softball Happy Face Tumbler Pouches</t>
-        </is>
-      </c>
-      <c r="D115" s="8" t="inlineStr">
-        <is>
-          <t>tumbler pouches</t>
-        </is>
-      </c>
-      <c r="E115" s="8" t="inlineStr">
-        <is>
-          <t>White Softball</t>
-        </is>
-      </c>
-      <c r="F115" s="8" t="inlineStr">
-        <is>
-          <t>The Softball Happy Face Tumbler Zipper Pouch is your new go-to accessory for a totally hands-free vibe! This pouch attaches right to your tumbler, so you can keep your essentials—like your phone, cards, or lip gloss—close by without the bulk of a bag. Perfect for when you're on the move, whether you're heading to the field or out with friends. Pair</t>
-        </is>
-      </c>
-      <c r="G115" s="8" t="inlineStr"/>
-      <c r="H115" s="8" t="inlineStr"/>
-      <c r="I115" s="8" t="inlineStr"/>
-      <c r="J115" s="8" t="inlineStr"/>
-      <c r="K115" s="8" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="6" t="n">
-        <v>115</v>
-      </c>
-      <c r="B116" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C116" s="8" t="inlineStr">
-        <is>
-          <t>Spring Flowers Tumbler Zipper Pouch</t>
-        </is>
-      </c>
-      <c r="D116" s="8" t="inlineStr">
-        <is>
-          <t>tumbler pouches</t>
-        </is>
-      </c>
-      <c r="E116" s="8" t="inlineStr">
-        <is>
-          <t>Multicolored Spring Florals</t>
-        </is>
-      </c>
-      <c r="F116" s="8" t="inlineStr">
-        <is>
-          <t>The Spring Flowers Tumbler Zipper Pouch is here to upgrade your hands-free game! Perfect for all those days when you need to carry the essentials but don’t want the bulk of a purse. This pouch keeps your phone, cards, makeup, and more safe and within reach, all while keeping you cute and organized. Want the full look? Pair it with the matching Spri</t>
-        </is>
-      </c>
-      <c r="G116" s="8" t="inlineStr"/>
-      <c r="H116" s="8" t="inlineStr"/>
-      <c r="I116" s="8" t="inlineStr"/>
-      <c r="J116" s="8" t="inlineStr"/>
-      <c r="K116" s="8" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="6" t="n">
-        <v>116</v>
-      </c>
-      <c r="B117" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C117" s="8" t="inlineStr">
-        <is>
-          <t>Strawberries Printed Attachable Tumbler Zipper Pouch</t>
-        </is>
-      </c>
-      <c r="D117" s="8" t="inlineStr">
-        <is>
-          <t>tumbler pouches</t>
-        </is>
-      </c>
-      <c r="E117" s="8" t="inlineStr">
-        <is>
-          <t>Peach Strawberry</t>
-        </is>
-      </c>
-      <c r="F117" s="8" t="inlineStr">
-        <is>
-          <t>Add a touch of sweetness and convenience to your tumbler with our Strawberries Printed Attachable Tumbler Zipper Pouch. This charming accessory, also known as a tumbler fanny pack or belt bag, is specifically designed to attach seamlessly to your tumbler cup, providing a stylish and practical solution for carrying your phone, wallet, and keys while</t>
-        </is>
-      </c>
-      <c r="G117" s="8" t="inlineStr"/>
-      <c r="H117" s="8" t="inlineStr"/>
-      <c r="I117" s="8" t="inlineStr"/>
-      <c r="J117" s="8" t="inlineStr"/>
-      <c r="K117" s="8" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="6" t="n">
-        <v>117</v>
-      </c>
-      <c r="B118" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C118" s="8" t="inlineStr">
-        <is>
-          <t>Subtle Strawberry Tumbler Zipper Pouch</t>
-        </is>
-      </c>
-      <c r="D118" s="8" t="inlineStr">
-        <is>
-          <t>tumbler pouches</t>
-        </is>
-      </c>
-      <c r="E118" s="8" t="inlineStr">
-        <is>
-          <t>Pink Strawberry</t>
-        </is>
-      </c>
-      <c r="F118" s="8" t="inlineStr">
-        <is>
-          <t>The Subtle Strawberry Tumbler Zipper Pouch is the ultimate hands-free solution you didn't know you needed. Whether you're heading to the gym, running errands, or just out and about, this cute tumbler pouch keeps all your essentials safe and easy to grab. Its minimal strawberry design makes it the perfect accessory for those who want to stay stylish</t>
-        </is>
-      </c>
-      <c r="G118" s="8" t="inlineStr"/>
-      <c r="H118" s="8" t="inlineStr"/>
-      <c r="I118" s="8" t="inlineStr"/>
-      <c r="J118" s="8" t="inlineStr"/>
-      <c r="K118" s="8" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="6" t="n">
-        <v>118</v>
-      </c>
-      <c r="B119" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C119" s="8" t="inlineStr">
-        <is>
-          <t>Sweet Orange Bag for Tumbler</t>
-        </is>
-      </c>
-      <c r="D119" s="8" t="inlineStr">
-        <is>
-          <t>tumbler pouches</t>
-        </is>
-      </c>
-      <c r="E119" s="8" t="inlineStr">
-        <is>
-          <t>Light Pink</t>
-        </is>
-      </c>
-      <c r="F119" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Your New Favorite Tumbler Zipper Bag for Sunny, Zesty Days If sunshine and a fruit stand had a baby, it would be this Sweet Orange Tumbler Pouch. This tumbler belt bag is bright, juicy, cheerful, and guaranteed to make your drink the cutest one in the room. Featuring adorable illustrated oranges and blossoms, it gives your tumbler instant “I’m fun </t>
-        </is>
-      </c>
-      <c r="G119" s="8" t="inlineStr"/>
-      <c r="H119" s="8" t="inlineStr"/>
-      <c r="I119" s="8" t="inlineStr"/>
-      <c r="J119" s="8" t="inlineStr"/>
-      <c r="K119" s="8" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="6" t="n">
-        <v>119</v>
-      </c>
-      <c r="B120" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C120" s="8" t="inlineStr">
-        <is>
-          <t>Whimsical Roses Tumbler Zipper Pouch</t>
-        </is>
-      </c>
-      <c r="D120" s="8" t="inlineStr">
-        <is>
-          <t>tumbler pouches</t>
-        </is>
-      </c>
-      <c r="E120" s="8" t="inlineStr">
-        <is>
-          <t>Light Pink</t>
-        </is>
-      </c>
-      <c r="F120" s="8" t="inlineStr">
-        <is>
-          <t>Blooming Cute: Your New Whimsical Roses Tumbler Pouch If springtime and girlhood teamed up to design the perfect hydration accessory, it would absolutely be this Whimsical Roses Tumbler Pouch. Bursting with playful pink blooms and leafy green details, this Tumbler Zipper Bag is basically a bouquet you don’t have to water. The adjustable velcro stra</t>
-        </is>
-      </c>
-      <c r="G120" s="8" t="inlineStr"/>
-      <c r="H120" s="8" t="inlineStr"/>
-      <c r="I120" s="8" t="inlineStr"/>
-      <c r="J120" s="8" t="inlineStr"/>
-      <c r="K120" s="8" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="6" t="n">
-        <v>120</v>
-      </c>
-      <c r="B121" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C121" s="8" t="inlineStr">
-        <is>
-          <t>Yellow and Aqua Striped Tumbler Zipper Pouch</t>
-        </is>
-      </c>
-      <c r="D121" s="8" t="inlineStr">
-        <is>
-          <t>tumbler pouches</t>
-        </is>
-      </c>
-      <c r="E121" s="8" t="inlineStr">
-        <is>
-          <t>Yellow and Aqua</t>
-        </is>
-      </c>
-      <c r="F121" s="8" t="inlineStr">
-        <is>
-          <t>Sip Cute, Store Cute: Your New Tumbler Zipper Bag Say hello to the Yellow and Aqua Striped Tumbler Pouch, AKA the tiny accessory with bold energy. This adorable Tumbler Zipper Bag attaches right onto your matching tumbler (sold separately), turning your hydration habit into a full-blown fashion moment. With its sunny-meets-seaside stripes, it’s bas</t>
-        </is>
-      </c>
-      <c r="G121" s="8" t="inlineStr"/>
-      <c r="H121" s="8" t="inlineStr"/>
-      <c r="I121" s="8" t="inlineStr"/>
-      <c r="J121" s="8" t="inlineStr"/>
-      <c r="K121" s="8" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="6" t="n">
-        <v>121</v>
-      </c>
-      <c r="B122" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C122" s="8" t="inlineStr">
-        <is>
-          <t>Zesty Lemons Tumbler Belt Bag</t>
-        </is>
-      </c>
-      <c r="D122" s="8" t="inlineStr">
-        <is>
-          <t>tumbler pouches</t>
-        </is>
-      </c>
-      <c r="E122" s="8" t="inlineStr">
-        <is>
-          <t>Light Blue</t>
-        </is>
-      </c>
-      <c r="F122" s="8" t="inlineStr">
-        <is>
-          <t>When Life Gives You Lemons… Accessorize Your Tumbler Bright, bold, and bursting with citrus personality, this Tumbler Zipper Bag is basically the wearable equivalent of a fresh summer spritz. It’s sunshine. It’s vacation energy. It’s “I’m fun, hydrated, and probably wearing cute sandals” energy. The adjustable velcro strap hugs your tumbler (matchi</t>
-        </is>
-      </c>
-      <c r="G122" s="8" t="inlineStr"/>
-      <c r="H122" s="8" t="inlineStr"/>
-      <c r="I122" s="8" t="inlineStr"/>
-      <c r="J122" s="8" t="inlineStr"/>
-      <c r="K122" s="8" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="6" t="n">
-        <v>122</v>
-      </c>
-      <c r="B123" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C123" s="8" t="inlineStr">
-        <is>
-          <t>American Bows 38 Oz Tumbler with Handle</t>
-        </is>
-      </c>
-      <c r="D123" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E123" s="8" t="inlineStr">
-        <is>
-          <t>White Flag Bows</t>
-        </is>
-      </c>
-      <c r="F123" s="8" t="inlineStr">
-        <is>
-          <t>Show your American pride while drinking your daily dose of water with the adorable American Bows tumbler. This 38 ounce cup is exactly what you need to carry around this election season!¬† 38 ounces includes reusable plastic straw all-day chill or heat stainless steel interior dishwasher safe screw-on plastic top with straw opening adjustable straw</t>
-        </is>
-      </c>
-      <c r="G123" s="8" t="inlineStr"/>
-      <c r="H123" s="8" t="inlineStr"/>
-      <c r="I123" s="8" t="inlineStr"/>
-      <c r="J123" s="8" t="inlineStr"/>
-      <c r="K123" s="8" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="6" t="n">
-        <v>123</v>
-      </c>
-      <c r="B124" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C124" s="8" t="inlineStr">
-        <is>
-          <t>American Flag &amp; Lips 38 Oz Tumbler Cup</t>
-        </is>
-      </c>
-      <c r="D124" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E124" s="8" t="inlineStr">
-        <is>
-          <t>White and Red Lips</t>
-        </is>
-      </c>
-      <c r="F124" s="8" t="inlineStr">
-        <is>
-          <t>Get ready to pucker up for patriotism with the American Flag &amp; Lips 38 Oz Tumbler Cup from Mimmolo. This striking white tumbler is not just a cup; it's a celebration of style, stars, and stripes. Emblazoned with American flag stripes, mini stars, and playful red and blue lips, this 38-ounce tumbler is the perfect accessory for those who want to sho</t>
-        </is>
-      </c>
-      <c r="G124" s="8" t="inlineStr"/>
-      <c r="H124" s="8" t="inlineStr"/>
-      <c r="I124" s="8" t="inlineStr"/>
-      <c r="J124" s="8" t="inlineStr"/>
-      <c r="K124" s="8" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="6" t="n">
-        <v>124</v>
-      </c>
-      <c r="B125" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C125" s="8" t="inlineStr">
-        <is>
-          <t>American Happy Face 38 Oz Tumbler Cup w/ Handle</t>
-        </is>
-      </c>
-      <c r="D125" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E125" s="8" t="inlineStr">
-        <is>
-          <t>White USA</t>
-        </is>
-      </c>
-      <c r="F125" s="8" t="inlineStr">
-        <is>
-          <t>Get ready to express your patriotic spirit in every sip with the American Happy Face 38 Oz Tumbler Cup w/ Handle, exclusively from Mimmolo.com. This large and stylish tumbler is not just a cup; it's a celebration of American pride and positivity. Featuring a vibrant design of happy faces adorned with the iconic stars and stripes, this tumbler is th</t>
-        </is>
-      </c>
-      <c r="G125" s="8" t="inlineStr"/>
-      <c r="H125" s="8" t="inlineStr"/>
-      <c r="I125" s="8" t="inlineStr"/>
-      <c r="J125" s="8" t="inlineStr"/>
-      <c r="K125" s="8" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="6" t="n">
-        <v>125</v>
-      </c>
-      <c r="B126" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C126" s="8" t="inlineStr">
-        <is>
-          <t>Aqua and Green Striped 30 Oz Cabana Tumbler</t>
-        </is>
-      </c>
-      <c r="D126" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E126" s="8" t="inlineStr">
-        <is>
-          <t>Aqua and Green</t>
-        </is>
-      </c>
-      <c r="F126" s="8" t="inlineStr">
-        <is>
-          <t>30 oz Travel Tumbler Cup in Aqua + Green Stripes If you’ve been waiting for a sign to upgrade your hydration game, this is it. Our aqua and green striped tumbler cup is here to add a splash of fun, function, and bold personality to your everyday routine. With a vibrant teal-and-green striped design, this 30 oz travel tumbler cup is giving total poo</t>
-        </is>
-      </c>
-      <c r="G126" s="8" t="inlineStr"/>
-      <c r="H126" s="8" t="inlineStr"/>
-      <c r="I126" s="8" t="inlineStr"/>
-      <c r="J126" s="8" t="inlineStr"/>
-      <c r="K126" s="8" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="6" t="n">
-        <v>126</v>
-      </c>
-      <c r="B127" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C127" s="8" t="inlineStr">
-        <is>
-          <t>Black &amp; Pink Mini Coquette Bows 38 Oz Tumbler w/ Handle</t>
-        </is>
-      </c>
-      <c r="D127" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E127" s="8" t="inlineStr">
-        <is>
-          <t>Black and Pink Bows</t>
-        </is>
-      </c>
-      <c r="F127" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pretty in Pink: Sip in Style with Our Pink Bow Tumbler Indulge in the hottest trend of the season with the pink bow tumbler exclusively from Mimmolo. Bows are taking the fashion world by storm, and this stainless steel tumbler cup is the epitome of coquettish charm, making it the perfect gift for trendsetters and style enthusiasts. Picture this: a </t>
-        </is>
-      </c>
-      <c r="G127" s="8" t="inlineStr"/>
-      <c r="H127" s="8" t="inlineStr"/>
-      <c r="I127" s="8" t="inlineStr"/>
-      <c r="J127" s="8" t="inlineStr"/>
-      <c r="K127" s="8" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="6" t="n">
-        <v>127</v>
-      </c>
-      <c r="B128" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C128" s="8" t="inlineStr">
-        <is>
-          <t>Black &amp; White Bows All Over Drink Tumbler Cup</t>
-        </is>
-      </c>
-      <c r="D128" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E128" s="8" t="inlineStr">
-        <is>
-          <t>Black and White Bows</t>
-        </is>
-      </c>
-      <c r="F128" s="8" t="inlineStr">
-        <is>
-          <t>A Bow Lover's Dream Tumbler is Here Sipping has never looked so chic. This Black &amp; White Bows Tumbler Cup gives you the perfect mix of elegance and playfulness. Made with durable stainless steel, it keeps your coffee hot and your look even hotter. The bold bow pattern is giving coquette queen energy, and we are here for it! Whether you're headed to</t>
-        </is>
-      </c>
-      <c r="G128" s="8" t="inlineStr"/>
-      <c r="H128" s="8" t="inlineStr"/>
-      <c r="I128" s="8" t="inlineStr"/>
-      <c r="J128" s="8" t="inlineStr"/>
-      <c r="K128" s="8" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="6" t="n">
-        <v>128</v>
-      </c>
-      <c r="B129" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C129" s="8" t="inlineStr">
-        <is>
-          <t>Black Coffee 40 Oz Tumbler with Handle</t>
-        </is>
-      </c>
-      <c r="D129" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E129" s="8" t="inlineStr">
-        <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="F129" s="8" t="inlineStr">
-        <is>
-          <t>Elevate your daily coffee routine with our Black Coffee 40 Oz Tumbler with Handle. Designed with style and practicality in mind, this sleek black tumbler is the perfect companion for coffee-loving men who appreciate both form and function. With its generous 40 Oz capacity, you can enjoy your favorite hot or iced beverages throughout the day, keepin</t>
-        </is>
-      </c>
-      <c r="G129" s="8" t="inlineStr"/>
-      <c r="H129" s="8" t="inlineStr"/>
-      <c r="I129" s="8" t="inlineStr"/>
-      <c r="J129" s="8" t="inlineStr"/>
-      <c r="K129" s="8" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="6" t="n">
-        <v>129</v>
-      </c>
-      <c r="B130" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C130" s="8" t="inlineStr">
-        <is>
-          <t>Black/White Cow Print Insulated Tumbler Cup with Handle</t>
-        </is>
-      </c>
-      <c r="D130" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E130" s="8" t="inlineStr">
-        <is>
-          <t>Black and White Cow</t>
-        </is>
-      </c>
-      <c r="F130" s="8" t="inlineStr">
-        <is>
-          <t>Get ready to ride off into the wild, wild west with Mimmolo's Cow Print 40 Oz Tumbler! This stainless steel tumbler is the perfect companion for fans of all things western. Adorned with a gorgeous cow print black and white pattern, you'll be ready to yee haw your way in style. The 40 oz tumbler features a convenient cup handle for you to grab onto,</t>
-        </is>
-      </c>
-      <c r="G130" s="8" t="inlineStr"/>
-      <c r="H130" s="8" t="inlineStr"/>
-      <c r="I130" s="8" t="inlineStr"/>
-      <c r="J130" s="8" t="inlineStr"/>
-      <c r="K130" s="8" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="6" t="n">
-        <v>130</v>
-      </c>
-      <c r="B131" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C131" s="8" t="inlineStr">
-        <is>
-          <t>Blue Insulated Tumbler Cup w/ Handle</t>
-        </is>
-      </c>
-      <c r="D131" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E131" s="8" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
-      <c r="F131" s="8" t="inlineStr">
-        <is>
-          <t>A new addition to the solid tumblers: a cool blue that matches the blue jean day. Sometimes you just need the basics. 40 ounces includes reusable plastic straw all-day chill or heat stainless steel interior dishwasher safe screw-on plastic top with straw opening adjustable straw cover for easy travel easy-to-hold handle fits in car cup holder (3" d</t>
-        </is>
-      </c>
-      <c r="G131" s="8" t="inlineStr"/>
-      <c r="H131" s="8" t="inlineStr"/>
-      <c r="I131" s="8" t="inlineStr"/>
-      <c r="J131" s="8" t="inlineStr"/>
-      <c r="K131" s="8" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="6" t="n">
-        <v>131</v>
-      </c>
-      <c r="B132" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C132" s="8" t="inlineStr">
-        <is>
-          <t>Bride Red Drawings 38 Oz Tumbler</t>
-        </is>
-      </c>
-      <c r="D132" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E132" s="8" t="inlineStr">
-        <is>
-          <t>Light Pink Bride</t>
-        </is>
-      </c>
-      <c r="F132" s="8" t="inlineStr">
-        <is>
-          <t>Ready to sip in style on your Big Day? Let us introduce you to Mimmolo's new Bride Red Drawings 38 Oz Tumbler! This tumbler is everything you need to celebrate the bride-to-be in style! Whether you're planning the ultimate bachelorette trip or treating yourself as the bride, this trendy stainless steel tumbler is your new best friend. With its bold</t>
-        </is>
-      </c>
-      <c r="G132" s="8" t="inlineStr"/>
-      <c r="H132" s="8" t="inlineStr"/>
-      <c r="I132" s="8" t="inlineStr"/>
-      <c r="J132" s="8" t="inlineStr"/>
-      <c r="K132" s="8" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="6" t="n">
-        <v>132</v>
-      </c>
-      <c r="B133" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C133" s="8" t="inlineStr">
-        <is>
-          <t>Cabana 38 Oz Tumbler with Handle (Pink and Orange Striped)</t>
-        </is>
-      </c>
-      <c r="D133" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E133" s="8" t="inlineStr">
-        <is>
-          <t>Pink and Orange</t>
-        </is>
-      </c>
-      <c r="F133" s="8" t="inlineStr">
-        <is>
-          <t>Hydration Upgrade: Pink + Orange Striped 38 oz Tumbler Jug Let’s be real — your hydration routine deserves an upgrade, and this pink + orange striped tumbler cup is here to deliver. At 38 oz, it’s oversized enough to keep you fueled through long workdays, workouts, or poolside lounging without constant refills. And it’s not just big — it’s brillian</t>
-        </is>
-      </c>
-      <c r="G133" s="8" t="inlineStr"/>
-      <c r="H133" s="8" t="inlineStr"/>
-      <c r="I133" s="8" t="inlineStr"/>
-      <c r="J133" s="8" t="inlineStr"/>
-      <c r="K133" s="8" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="6" t="n">
-        <v>133</v>
-      </c>
-      <c r="B134" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C134" s="8" t="inlineStr">
-        <is>
-          <t>Camo Print Tumbler Cup with Straw</t>
-        </is>
-      </c>
-      <c r="D134" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E134" s="8" t="inlineStr">
-        <is>
-          <t>Camo</t>
-        </is>
-      </c>
-      <c r="F134" s="8" t="inlineStr">
-        <is>
-          <t>Hey there, guys! Say hello to the Camo Print Tumbler Cup with Straw, the must-have accessory for the modern man. This rugged and stylish tumbler is designed to keep up with your active lifestyle while adding a touch of cool camo vibes to your everyday routine. Featuring a sleek camo print, this tumbler is the perfect blend of fashion and functional</t>
-        </is>
-      </c>
-      <c r="G134" s="8" t="inlineStr"/>
-      <c r="H134" s="8" t="inlineStr"/>
-      <c r="I134" s="8" t="inlineStr"/>
-      <c r="J134" s="8" t="inlineStr"/>
-      <c r="K134" s="8" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="6" t="n">
-        <v>134</v>
-      </c>
-      <c r="B135" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C135" s="8" t="inlineStr">
-        <is>
-          <t>Dainty Florals Pink 38 Oz Tumbler Cup</t>
-        </is>
-      </c>
-      <c r="D135" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E135" s="8" t="inlineStr">
-        <is>
-          <t>Light Pink and Blue Flowers</t>
-        </is>
-      </c>
-      <c r="F135" s="8" t="inlineStr">
-        <is>
-          <t>Stay hydrated in style with the Dainty Florals Pink 38 Oz Tumbler! This adorable pink tumbler isn’t just a pretty face; it’s got all the features you need to make drinking water a total vibe. With a sturdy handle for easy carrying, it fits right in your car cup holder (because yes, you can have both style and function). And don’t worry about the cl</t>
-        </is>
-      </c>
-      <c r="G135" s="8" t="inlineStr"/>
-      <c r="H135" s="8" t="inlineStr"/>
-      <c r="I135" s="8" t="inlineStr"/>
-      <c r="J135" s="8" t="inlineStr"/>
-      <c r="K135" s="8" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="6" t="n">
-        <v>135</v>
-      </c>
-      <c r="B136" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C136" s="8" t="inlineStr">
-        <is>
-          <t>Deer All Over Black Tumbler for Men</t>
-        </is>
-      </c>
-      <c r="D136" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E136" s="8" t="inlineStr">
-        <is>
-          <t>Black Deer</t>
-        </is>
-      </c>
-      <c r="F136" s="8" t="inlineStr">
-        <is>
-          <t>Hey, guys! Looking for a stylish tumbler that combines rugged charm with sleek design? Look no further than the Deer All Over Black Tumbler for Men, available at Mimmolo.com. This black tumbler exudes a confident vibe with its metallic silver deer design, adding a touch of sophistication to your daily routine. Crafted with care and attention to det</t>
-        </is>
-      </c>
-      <c r="G136" s="8" t="inlineStr"/>
-      <c r="H136" s="8" t="inlineStr"/>
-      <c r="I136" s="8" t="inlineStr"/>
-      <c r="J136" s="8" t="inlineStr"/>
-      <c r="K136" s="8" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="6" t="n">
-        <v>136</v>
-      </c>
-      <c r="B137" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C137" s="8" t="inlineStr">
-        <is>
-          <t>Fall Bears 38 Oz Tumbler with Lid Handle</t>
-        </is>
-      </c>
-      <c r="D137" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E137" s="8" t="inlineStr">
-        <is>
-          <t>Light Blue Teddy Bears</t>
-        </is>
-      </c>
-      <c r="F137" s="8" t="inlineStr">
-        <is>
-          <t>Sips and Snuggles: Your Cozy Bear Tumbler Cup Cuddle up with your new favorite tumbler cup! The Fall Bears 38 oz Tumbler is the definition of cozy girl energy, featuring an adorable teddy bear print, sturdy handle, and secure lid. It’s the ultimate companion for pumpkin patches, cozy couch hangs, and your never-ending to-do list. Whether you’re run</t>
-        </is>
-      </c>
-      <c r="G137" s="8" t="inlineStr"/>
-      <c r="H137" s="8" t="inlineStr"/>
-      <c r="I137" s="8" t="inlineStr"/>
-      <c r="J137" s="8" t="inlineStr"/>
-      <c r="K137" s="8" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="6" t="n">
-        <v>137</v>
-      </c>
-      <c r="B138" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C138" s="8" t="inlineStr">
-        <is>
-          <t>Fishing Lures Tumbler Cup with Handle</t>
-        </is>
-      </c>
-      <c r="D138" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E138" s="8" t="inlineStr">
-        <is>
-          <t>Black Fish</t>
-        </is>
-      </c>
-      <c r="F138" s="8" t="inlineStr">
-        <is>
-          <t>Reel in the perfect gift for the angler in your life with our Fishing Lures Tumbler Cup. Designed for the outdoorsman who cherishes every moment by the water, this sleek black tumbler features an array of vibrant fishing lures. It's not just a drink holder; it's an expression of passion for fishing. Crafted with durable stainless steel, this tumble</t>
-        </is>
-      </c>
-      <c r="G138" s="8" t="inlineStr"/>
-      <c r="H138" s="8" t="inlineStr"/>
-      <c r="I138" s="8" t="inlineStr"/>
-      <c r="J138" s="8" t="inlineStr"/>
-      <c r="K138" s="8" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="6" t="n">
-        <v>138</v>
-      </c>
-      <c r="B139" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C139" s="8" t="inlineStr">
-        <is>
-          <t>Groovy Multicolored Flowers Tumbler Cup</t>
-        </is>
-      </c>
-      <c r="D139" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E139" s="8" t="inlineStr">
-        <is>
-          <t>Light Pink</t>
-        </is>
-      </c>
-      <c r="F139" s="8" t="inlineStr">
-        <is>
-          <t>Sip in Full Color — The Groovy Retro Stainless Steel Tumbler If sunshine had a drink cup, this would be it. The Groovy Multicolored Flowers Tumbler Cup brings all the retro-flower-power vibes to your daily sips, whether you’re lounging by the pool, running errands, or vibing through a summer road trip with the windows down. Packed with bright color</t>
-        </is>
-      </c>
-      <c r="G139" s="8" t="inlineStr"/>
-      <c r="H139" s="8" t="inlineStr"/>
-      <c r="I139" s="8" t="inlineStr"/>
-      <c r="J139" s="8" t="inlineStr"/>
-      <c r="K139" s="8" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="6" t="n">
-        <v>139</v>
-      </c>
-      <c r="B140" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C140" s="8" t="inlineStr">
-        <is>
-          <t>In My Cheer Era 38 Oz Tumbler with Lid Handle</t>
-        </is>
-      </c>
-      <c r="D140" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E140" s="8" t="inlineStr">
-        <is>
-          <t>Pink Cheer</t>
-        </is>
-      </c>
-      <c r="F140" s="8" t="inlineStr">
-        <is>
-          <t>Show off your cheer spirit, on and off the mat. Mimmolo's "In My Cheer Era" tumbler is the ultimate accessory for cheerleaders who need to stay hydrated during their busy schedules. With a convenient top lid handle and a side handle, you can easily grab it while practicing your stunts or cheering on your team. Plus, it fits perfectly in a cup holde</t>
-        </is>
-      </c>
-      <c r="G140" s="8" t="inlineStr"/>
-      <c r="H140" s="8" t="inlineStr"/>
-      <c r="I140" s="8" t="inlineStr"/>
-      <c r="J140" s="8" t="inlineStr"/>
-      <c r="K140" s="8" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="6" t="n">
-        <v>140</v>
-      </c>
-      <c r="B141" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C141" s="8" t="inlineStr">
-        <is>
-          <t>Jug Tumbler Handle Lid Replacements</t>
-        </is>
-      </c>
-      <c r="D141" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E141" s="8" t="inlineStr">
-        <is>
-          <t>White, Light Pink, Pink, Green</t>
-        </is>
-      </c>
-      <c r="F141" s="8" t="inlineStr">
-        <is>
-          <t>Screw-in top Lid fits on our 40 oz tumblers and 38 oz tumblers Try our unique ridged tumbler lids or our classic clear lids ! * straw sold separately</t>
-        </is>
-      </c>
-      <c r="G141" s="8" t="inlineStr"/>
-      <c r="H141" s="8" t="inlineStr"/>
-      <c r="I141" s="8" t="inlineStr"/>
-      <c r="J141" s="8" t="inlineStr"/>
-      <c r="K141" s="8" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="6" t="n">
-        <v>141</v>
-      </c>
-      <c r="B142" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C142" s="8" t="inlineStr">
-        <is>
-          <t>Light Blue and Navy Striped 30 Oz Tumbler Cup</t>
-        </is>
-      </c>
-      <c r="D142" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E142" s="8" t="inlineStr">
-        <is>
-          <t>Light Blue and Navy</t>
-        </is>
-      </c>
-      <c r="F142" s="8" t="inlineStr">
-        <is>
-          <t>Standout Light Blue and Navy Striped Tumbler Cup for On-the-Go Style Hydration just got a major upgrade. Our blue and navy striped tumbler cup is the ultimate mix of bold design, everyday function, and “yes, I need that” energy. Made for the girl who wants her morning iced latte to stay cold until her afternoon conference call, this cute 30 oz trav</t>
-        </is>
-      </c>
-      <c r="G142" s="8" t="inlineStr"/>
-      <c r="H142" s="8" t="inlineStr"/>
-      <c r="I142" s="8" t="inlineStr"/>
-      <c r="J142" s="8" t="inlineStr"/>
-      <c r="K142" s="8" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="6" t="n">
-        <v>142</v>
-      </c>
-      <c r="B143" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C143" s="8" t="inlineStr">
-        <is>
-          <t>Light Blue and Navy Striped Tumbler With Handle</t>
-        </is>
-      </c>
-      <c r="D143" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E143" s="8" t="inlineStr">
-        <is>
-          <t>Light Blue and Navy</t>
-        </is>
-      </c>
-      <c r="F143" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bold Blue 38 oz Striped Tumbler Cup with Straw Not all tumblers are created equal — and this one proves it. Our 38 oz blue striped tumbler cup is designed for people who want their drinkware to stand out while still delivering all the function they need. With bold navy-and-light blue stripes, it’s not just a tumbler — it’s a style statement you’ll </t>
-        </is>
-      </c>
-      <c r="G143" s="8" t="inlineStr"/>
-      <c r="H143" s="8" t="inlineStr"/>
-      <c r="I143" s="8" t="inlineStr"/>
-      <c r="J143" s="8" t="inlineStr"/>
-      <c r="K143" s="8" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="6" t="n">
-        <v>143</v>
-      </c>
-      <c r="B144" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C144" s="8" t="inlineStr">
-        <is>
-          <t>Lobsters Tumbler Cup</t>
-        </is>
-      </c>
-      <c r="D144" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E144" s="8" t="inlineStr">
-        <is>
-          <t>Pink</t>
-        </is>
-      </c>
-      <c r="F144" s="8" t="inlineStr">
-        <is>
-          <t>Beachy and Bright Lobster Print Travel Tumbler If you love a good coastal moment, the Lobsters Tumbler Cup is about to become your new warm-weather favorite. Designed with a bold, bright lobster print and crafted for long days in the sun, this tumbler with straw brings a fun, summery touch to every sip. It blends beach-town energy with everyday fun</t>
-        </is>
-      </c>
-      <c r="G144" s="8" t="inlineStr"/>
-      <c r="H144" s="8" t="inlineStr"/>
-      <c r="I144" s="8" t="inlineStr"/>
-      <c r="J144" s="8" t="inlineStr"/>
-      <c r="K144" s="8" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="6" t="n">
-        <v>144</v>
-      </c>
-      <c r="B145" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C145" s="8" t="inlineStr">
-        <is>
-          <t>Lucky Girl Western 38 Oz Tumbler</t>
-        </is>
-      </c>
-      <c r="D145" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E145" s="8" t="inlineStr">
-        <is>
-          <t>Lucky Mint</t>
-        </is>
-      </c>
-      <c r="F145" s="8" t="inlineStr">
-        <is>
-          <t>Calling all Nashville-loving babes! This western-inspired 38 oz. stainless steel tumbler features a light blue background with trendy illustrations, including rainbows, dice, cowboy boots, and horseshoes, giving off a cool, carefree cowgirl vibe. Pair it with a matching trucker hat or accessories for a complete look that will have people saying, "O</t>
-        </is>
-      </c>
-      <c r="G145" s="8" t="inlineStr"/>
-      <c r="H145" s="8" t="inlineStr"/>
-      <c r="I145" s="8" t="inlineStr"/>
-      <c r="J145" s="8" t="inlineStr"/>
-      <c r="K145" s="8" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="6" t="n">
-        <v>145</v>
-      </c>
-      <c r="B146" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C146" s="8" t="inlineStr">
-        <is>
-          <t>Mahjong Pieces Hydration Tumbler</t>
-        </is>
-      </c>
-      <c r="D146" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E146" s="8" t="inlineStr">
-        <is>
-          <t>Light Pink</t>
-        </is>
-      </c>
-      <c r="F146" s="8" t="inlineStr">
-        <is>
-          <t>Mahjong Lover Tumbler Cup for Everyday If mahjong night is your personality and your group chat is always planning the next game, this Mimmolo tumbler belongs to you. The Mahjong Pieces Flip Top Tumbler brings that fun, social energy into your everyday routine. Featuring a playful mix of tiles, florals, and girly details, it feels niche in the best</t>
-        </is>
-      </c>
-      <c r="G146" s="8" t="inlineStr"/>
-      <c r="H146" s="8" t="inlineStr"/>
-      <c r="I146" s="8" t="inlineStr"/>
-      <c r="J146" s="8" t="inlineStr"/>
-      <c r="K146" s="8" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="6" t="n">
-        <v>146</v>
-      </c>
-      <c r="B147" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C147" s="8" t="inlineStr">
-        <is>
-          <t>Men's Navy Water Tumbler Cup</t>
-        </is>
-      </c>
-      <c r="D147" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E147" s="8" t="inlineStr">
-        <is>
-          <t>Navy</t>
-        </is>
-      </c>
-      <c r="F147" s="8" t="inlineStr">
-        <is>
-          <t>Hey guys! Introducing the ultimate hydration solution for the modern man - the Men's Navy Water Tumbler Cup. Designed to keep you refreshed and hydrated throughout the day, this sleek navy blue tumbler is a game-changer when it comes to staying cool, calm, and collected. With its generous 40 Oz capacity, this tumbler has got your hydration needs co</t>
-        </is>
-      </c>
-      <c r="G147" s="8" t="inlineStr"/>
-      <c r="H147" s="8" t="inlineStr"/>
-      <c r="I147" s="8" t="inlineStr"/>
-      <c r="J147" s="8" t="inlineStr"/>
-      <c r="K147" s="8" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="6" t="n">
-        <v>147</v>
-      </c>
-      <c r="B148" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C148" s="8" t="inlineStr">
-        <is>
-          <t>Multicolored Coquette Bows 38 Oz Tumbler w/ Handle</t>
-        </is>
-      </c>
-      <c r="D148" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E148" s="8" t="inlineStr">
-        <is>
-          <t>Multicolored Bows</t>
-        </is>
-      </c>
-      <c r="F148" s="8" t="inlineStr">
-        <is>
-          <t>Add Some Flair to Your Sip with Our Bow Tumbler! Bow-tifully hydrated, anyone? Embrace the latest coquette trend with our new multi-colored tumbler . Featuring a vibrant, playful design, this bow tumbler is perfect for adding a girly touch to your day. You can enjoy the large 38 oz capacity that ensures you'll stay refreshed all day long. This tumb</t>
-        </is>
-      </c>
-      <c r="G148" s="8" t="inlineStr"/>
-      <c r="H148" s="8" t="inlineStr"/>
-      <c r="I148" s="8" t="inlineStr"/>
-      <c r="J148" s="8" t="inlineStr"/>
-      <c r="K148" s="8" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="6" t="n">
-        <v>148</v>
-      </c>
-      <c r="B149" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C149" s="8" t="inlineStr">
-        <is>
-          <t>Multicolored Hearts Mint Tumbler Cup w/ Handle</t>
-        </is>
-      </c>
-      <c r="D149" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E149" s="8" t="inlineStr">
-        <is>
-          <t>Mint Hearts</t>
-        </is>
-      </c>
-      <c r="F149" s="8" t="inlineStr">
-        <is>
-          <t>Valentine's Day ready with an adorable mint tumbler with colorful hearts all over it! Tell your boyfriend to get this for you for Valentine's Day. Or equip your Galentine's Day with this one. Whichever you choose, they're going to love it. 38 ounces includes reusable plastic straw all-day chill or heat stainless steel interior dishwasher safe screw</t>
-        </is>
-      </c>
-      <c r="G149" s="8" t="inlineStr"/>
-      <c r="H149" s="8" t="inlineStr"/>
-      <c r="I149" s="8" t="inlineStr"/>
-      <c r="J149" s="8" t="inlineStr"/>
-      <c r="K149" s="8" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="6" t="n">
-        <v>149</v>
-      </c>
-      <c r="B150" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C150" s="8" t="inlineStr">
-        <is>
-          <t>Music Girl Icons Drink Tumbler</t>
-        </is>
-      </c>
-      <c r="D150" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E150" s="8" t="inlineStr">
-        <is>
-          <t>Light Pink Music Girl</t>
-        </is>
-      </c>
-      <c r="F150" s="8" t="inlineStr">
-        <is>
-          <t>Shake it off and stay hydrated with Mimmolo's new stainless steel tumbler! Whether you're chasing your wildest dreams or looking to be hydrated all to well, this music icon stainless steel tumbler is everything. Featuring iconic references from chart-topping hits, this travel tumbler cup is your perfect match for sipping all day. Whether you're dan</t>
-        </is>
-      </c>
-      <c r="G150" s="8" t="inlineStr"/>
-      <c r="H150" s="8" t="inlineStr"/>
-      <c r="I150" s="8" t="inlineStr"/>
-      <c r="J150" s="8" t="inlineStr"/>
-      <c r="K150" s="8" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="6" t="n">
-        <v>150</v>
-      </c>
-      <c r="B151" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C151" s="8" t="inlineStr">
-        <is>
-          <t>Navy Daisy Tumbler Cup with Handle</t>
-        </is>
-      </c>
-      <c r="D151" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E151" s="8" t="inlineStr">
-        <is>
-          <t>Navy Daisy</t>
-        </is>
-      </c>
-      <c r="F151" s="8" t="inlineStr">
-        <is>
-          <t>Add a little sunshine to your days with the Groovy Daisy Tumbler from Mimmolo! Want to get away from those ordinary tumblers? The Groovy Daisy Tumbler brings a pop of color and fun to any day. This 40-ounce navy tumbler, complete with an easy-to-hold handle, is made for on-the-go sipping. Featuring colorful florals and comes with its own drinking s</t>
-        </is>
-      </c>
-      <c r="G151" s="8" t="inlineStr"/>
-      <c r="H151" s="8" t="inlineStr"/>
-      <c r="I151" s="8" t="inlineStr"/>
-      <c r="J151" s="8" t="inlineStr"/>
-      <c r="K151" s="8" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="6" t="n">
-        <v>151</v>
-      </c>
-      <c r="B152" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C152" s="8" t="inlineStr">
-        <is>
-          <t>Pickleball Social Club 38 Oz Tumbler with Lid Handle</t>
-        </is>
-      </c>
-      <c r="D152" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E152" s="8" t="inlineStr">
-        <is>
-          <t>Preppy Light Pink and Green</t>
-        </is>
-      </c>
-      <c r="F152" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ready to serve up style and stay hydrated? Ace your hydration game with the new Mimmolo Pickleball Social Club 38 Oz Tumbler with Lid &amp; Handle. This stainless steel tumbler is here to keep your drinks chill during every pickleball game and beyond! With a secure lid to keep spills in check and a handle for easy carry, this tumbler fits perfectly in </t>
-        </is>
-      </c>
-      <c r="G152" s="8" t="inlineStr"/>
-      <c r="H152" s="8" t="inlineStr"/>
-      <c r="I152" s="8" t="inlineStr"/>
-      <c r="J152" s="8" t="inlineStr"/>
-      <c r="K152" s="8" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="6" t="n">
-        <v>152</v>
-      </c>
-      <c r="B153" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C153" s="8" t="inlineStr">
-        <is>
-          <t>Pink Purple Green Swirl Tumbler Cup</t>
-        </is>
-      </c>
-      <c r="D153" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E153" s="8" t="inlineStr">
-        <is>
-          <t>Light Pink and Purple Swirl</t>
-        </is>
-      </c>
-      <c r="F153" s="8" t="inlineStr">
-        <is>
-          <t>Swirls are so in. This pink, purple and green mix is the perfect fall touch to a good 38 oz tumbler. Each tumbler by Mimmolo comes with a matching lid and straw. Perfect as a gift, or for yourself! 38 ounces includes reusable plastic straw all-day chill or heat stainless steel interior dishwasher safe screw-on plastic top with straw opening adjusta</t>
-        </is>
-      </c>
-      <c r="G153" s="8" t="inlineStr"/>
-      <c r="H153" s="8" t="inlineStr"/>
-      <c r="I153" s="8" t="inlineStr"/>
-      <c r="J153" s="8" t="inlineStr"/>
-      <c r="K153" s="8" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="6" t="n">
-        <v>153</v>
-      </c>
-      <c r="B154" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C154" s="8" t="inlineStr">
-        <is>
-          <t>Pink Santas 38 Oz Tumbler</t>
-        </is>
-      </c>
-      <c r="D154" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E154" s="8" t="inlineStr">
-        <is>
-          <t>Light Pink Santa</t>
-        </is>
-      </c>
-      <c r="F154" s="8" t="inlineStr">
-        <is>
-          <t>Sleigh All Day with This Pink Santa Tumbler Cup Calling all holiday lovers— this Pink Santa Tumbler Cup is pure Christmas cheer! Whether you're sipping hot cocoa while wrapping gifts or iced coffee on the go, this stainless steel tumbler keeps your drinks at the perfect temp. The pink Santa print adds just the right touch of girly holiday magic. Wi</t>
-        </is>
-      </c>
-      <c r="G154" s="8" t="inlineStr"/>
-      <c r="H154" s="8" t="inlineStr"/>
-      <c r="I154" s="8" t="inlineStr"/>
-      <c r="J154" s="8" t="inlineStr"/>
-      <c r="K154" s="8" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="6" t="n">
-        <v>154</v>
-      </c>
-      <c r="B155" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C155" s="8" t="inlineStr">
-        <is>
-          <t>Pink and Hot Pink Striped Drink Tumbler</t>
-        </is>
-      </c>
-      <c r="D155" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E155" s="8" t="inlineStr">
-        <is>
-          <t>Pink and Hot Pink</t>
-        </is>
-      </c>
-      <c r="F155" s="8" t="inlineStr">
-        <is>
-          <t>Everyday Essential: 38 oz Pink Striped Tumbler Cup Meet the tumbler that’s about to take center stage in your daily routine. Our 38 oz pink striped tumbler cup is not just a cup, it’s a statement piece for your desk, car, or poolside setup. With its playful pink-on-pink vertical stripes, it’s chic enough to match your vibe while being practical eno</t>
-        </is>
-      </c>
-      <c r="G155" s="8" t="inlineStr"/>
-      <c r="H155" s="8" t="inlineStr"/>
-      <c r="I155" s="8" t="inlineStr"/>
-      <c r="J155" s="8" t="inlineStr"/>
-      <c r="K155" s="8" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="6" t="n">
-        <v>155</v>
-      </c>
-      <c r="B156" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C156" s="8" t="inlineStr">
-        <is>
-          <t>Pink and Orange Striped 30 Oz Tumbler Cup</t>
-        </is>
-      </c>
-      <c r="D156" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E156" s="8" t="inlineStr">
-        <is>
-          <t>Pink and Orange</t>
-        </is>
-      </c>
-      <c r="F156" s="8" t="inlineStr">
-        <is>
-          <t>Sip Happy with Our Pink and Orange Striped Travel Tumbler Cup Some days call for more than basic black — they call for color. Meet the pink and orange striped tumbler cup, designed for anyone who wants hydration with a side of fun. This travel tumbler cup isn’t just a pretty face; it’s insulated, comes with a sturdy handle, and keeps your drinks pe</t>
-        </is>
-      </c>
-      <c r="G156" s="8" t="inlineStr"/>
-      <c r="H156" s="8" t="inlineStr"/>
-      <c r="I156" s="8" t="inlineStr"/>
-      <c r="J156" s="8" t="inlineStr"/>
-      <c r="K156" s="8" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="6" t="n">
-        <v>156</v>
-      </c>
-      <c r="B157" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C157" s="8" t="inlineStr">
-        <is>
-          <t>Pink and Wine Striped 30 Oz Cabana Tumbler</t>
-        </is>
-      </c>
-      <c r="D157" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E157" s="8" t="inlineStr">
-        <is>
-          <t>Pink and Wine</t>
-        </is>
-      </c>
-      <c r="F157" s="8" t="inlineStr">
-        <is>
-          <t>Pink Striped Tumbler Cup for Cute Hydration Goals Because boring cups just won’t cut it anymore. Our pink striped tumbler cup is here to upgrade your hydration game with major cuteness and practicality. Designed with candy-colored stripes, this travel tumbler cup is double-walled, insulated, and complete with a sturdy handle for easy carrying. Perf</t>
-        </is>
-      </c>
-      <c r="G157" s="8" t="inlineStr"/>
-      <c r="H157" s="8" t="inlineStr"/>
-      <c r="I157" s="8" t="inlineStr"/>
-      <c r="J157" s="8" t="inlineStr"/>
-      <c r="K157" s="8" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="6" t="n">
-        <v>157</v>
-      </c>
-      <c r="B158" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C158" s="8" t="inlineStr">
-        <is>
-          <t>Plum Tumbler Cup w/ Handle</t>
-        </is>
-      </c>
-      <c r="D158" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E158" s="8" t="inlineStr">
-        <is>
-          <t>Plum</t>
-        </is>
-      </c>
-      <c r="F158" s="8" t="inlineStr">
-        <is>
-          <t>Finally! A plum purple tumbler cup that will retain ice overnight. This 40 oz tumbler cup comes with a handle, a plastic straw and a matching lid. More solid colors to love! 40 ounces includes reusable plastic straw all-day chill or heat stainless steel interior dishwasher safe screw-on plastic top with straw opening adjustable straw cover for easy</t>
-        </is>
-      </c>
-      <c r="G158" s="8" t="inlineStr"/>
-      <c r="H158" s="8" t="inlineStr"/>
-      <c r="I158" s="8" t="inlineStr"/>
-      <c r="J158" s="8" t="inlineStr"/>
-      <c r="K158" s="8" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="6" t="n">
-        <v>158</v>
-      </c>
-      <c r="B159" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C159" s="8" t="inlineStr">
-        <is>
-          <t>Queen of the Green Golf 38 Oz Tumbler with Lid Handle</t>
-        </is>
-      </c>
-      <c r="D159" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E159" s="8" t="inlineStr">
-        <is>
-          <t>Golf Green</t>
-        </is>
-      </c>
-      <c r="F159" s="8" t="inlineStr">
-        <is>
-          <t>Swing into style with the Queen of the Green Golf 38 Oz Tumbler! ⛳️ For all the golf lovers out there, this Queen of the Green Golf 38 Oz Tumbler is your new go-to for staying hydrated while you slay the course. With a sleek design, it features both a top lid and a side handle, making it easy to carry and sip between swings. The 38 oz capacity mean</t>
-        </is>
-      </c>
-      <c r="G159" s="8" t="inlineStr"/>
-      <c r="H159" s="8" t="inlineStr"/>
-      <c r="I159" s="8" t="inlineStr"/>
-      <c r="J159" s="8" t="inlineStr"/>
-      <c r="K159" s="8" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="6" t="n">
-        <v>159</v>
-      </c>
-      <c r="B160" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C160" s="8" t="inlineStr">
-        <is>
-          <t>Replacement Tumbler Lids</t>
-        </is>
-      </c>
-      <c r="D160" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E160" s="8" t="inlineStr">
-        <is>
-          <t>Orchid, White, Mint, Light Blue, Hot Pink</t>
-        </is>
-      </c>
-      <c r="F160" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Are you a chic girl looking for the perfect replacement lid to go with your 40 oz tumbler cup? Look no further, because you've just found it! Mimmolo has the perfect Tumbler Lid Replacement for you that will instantly transform your old and average cup into something amazing. Accidents happen, but now they're not such a problem! Let it be dropping </t>
-        </is>
-      </c>
-      <c r="G160" s="8" t="inlineStr"/>
-      <c r="H160" s="8" t="inlineStr"/>
-      <c r="I160" s="8" t="inlineStr"/>
-      <c r="J160" s="8" t="inlineStr"/>
-      <c r="K160" s="8" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="6" t="n">
-        <v>160</v>
-      </c>
-      <c r="B161" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C161" s="8" t="inlineStr">
-        <is>
-          <t>Ridged Tumbler Lid Replacements</t>
-        </is>
-      </c>
-      <c r="D161" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E161" s="8" t="inlineStr">
-        <is>
-          <t>White, Pink, Light Blue, Mint, Light Pink</t>
-        </is>
-      </c>
-      <c r="F161" s="8" t="inlineStr">
-        <is>
-          <t>Screw-in top Lid fits on our 40 oz tumblers and 38 oz tumblers Try our top handle jug lids or our classic clear lids !</t>
-        </is>
-      </c>
-      <c r="G161" s="8" t="inlineStr"/>
-      <c r="H161" s="8" t="inlineStr"/>
-      <c r="I161" s="8" t="inlineStr"/>
-      <c r="J161" s="8" t="inlineStr"/>
-      <c r="K161" s="8" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="6" t="n">
-        <v>161</v>
-      </c>
-      <c r="B162" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C162" s="8" t="inlineStr">
-        <is>
-          <t>Rose Pink Drink Tumbler Cup w/ Handle</t>
-        </is>
-      </c>
-      <c r="D162" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E162" s="8" t="inlineStr">
-        <is>
-          <t>Rose Pink</t>
-        </is>
-      </c>
-      <c r="F162" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">We love a pink pink pink girl. And now we have another shade of pink to add to our solid tumblers inventory! This soft rose pink tumbler holds 40 ounces of water, retains heat or cold overnight, and has a handle to easily hold. 40 ounces includes reusable plastic straw all-day chill or heat stainless steel interior dishwasher safe screw-on plastic </t>
-        </is>
-      </c>
-      <c r="G162" s="8" t="inlineStr"/>
-      <c r="H162" s="8" t="inlineStr"/>
-      <c r="I162" s="8" t="inlineStr"/>
-      <c r="J162" s="8" t="inlineStr"/>
-      <c r="K162" s="8" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="6" t="n">
-        <v>162</v>
-      </c>
-      <c r="B163" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C163" s="8" t="inlineStr">
-        <is>
-          <t>Santa Claus Repeat Holiday Tumbler Cup</t>
-        </is>
-      </c>
-      <c r="D163" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E163" s="8" t="inlineStr">
-        <is>
-          <t>Pink and Red Santa</t>
-        </is>
-      </c>
-      <c r="F163" s="8" t="inlineStr">
-        <is>
-          <t>Make your holiday season extra jolly with the Santa Claus Repeat Holiday Tumbler Cup from Mimmolo.com. This adorable pink tumbler is adorned with an abundance of cheerful Santa Claus designs, bringing a festive and whimsical touch to your drinkware collection. With its convenient handle and included straw, this tumbler is perfect for young women wh</t>
-        </is>
-      </c>
-      <c r="G163" s="8" t="inlineStr"/>
-      <c r="H163" s="8" t="inlineStr"/>
-      <c r="I163" s="8" t="inlineStr"/>
-      <c r="J163" s="8" t="inlineStr"/>
-      <c r="K163" s="8" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="6" t="n">
-        <v>163</v>
-      </c>
-      <c r="B164" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C164" s="8" t="inlineStr">
-        <is>
-          <t>Skull Flower Bow Drink Tumbler</t>
-        </is>
-      </c>
-      <c r="D164" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E164" s="8" t="inlineStr">
-        <is>
-          <t>Light Pink Skull Flowers</t>
-        </is>
-      </c>
-      <c r="F164" s="8" t="inlineStr">
-        <is>
-          <t>Gen Z is going to love this. Skulls. Flowers. Coquette bows. We're mixing all things trending for the young demographic. Plus it's perfect around Halloween. We all had our emo girl era... right? 38 ounces includes reusable plastic straw all-day chill or heat stainless steel interior dishwasher safe screw-on plastic top with straw opening adjustable</t>
-        </is>
-      </c>
-      <c r="G164" s="8" t="inlineStr"/>
-      <c r="H164" s="8" t="inlineStr"/>
-      <c r="I164" s="8" t="inlineStr"/>
-      <c r="J164" s="8" t="inlineStr"/>
-      <c r="K164" s="8" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="6" t="n">
-        <v>164</v>
-      </c>
-      <c r="B165" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C165" s="8" t="inlineStr">
-        <is>
-          <t>Softball Happy Face 40 Oz Tumbler</t>
-        </is>
-      </c>
-      <c r="D165" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E165" s="8" t="inlineStr">
-        <is>
-          <t>White Softball</t>
-        </is>
-      </c>
-      <c r="F165" s="8" t="inlineStr">
-        <is>
-          <t>Hit a home run with the Softball Happy Face 40 Oz Tumbler! This large stainless steel tumbler is all about bringing the good vibes and staying hydrated, whether you're on the field or chilling off the clock. Featuring an adorable smiley face and bold design, this tumbler is your new best friend for every game day and beyond. With a massive 40 oz ca</t>
-        </is>
-      </c>
-      <c r="G165" s="8" t="inlineStr"/>
-      <c r="H165" s="8" t="inlineStr"/>
-      <c r="I165" s="8" t="inlineStr"/>
-      <c r="J165" s="8" t="inlineStr"/>
-      <c r="K165" s="8" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="6" t="n">
-        <v>165</v>
-      </c>
-      <c r="B166" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C166" s="8" t="inlineStr">
-        <is>
-          <t>Spring Flowers Tumbler with Handle</t>
-        </is>
-      </c>
-      <c r="D166" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E166" s="8" t="inlineStr">
-        <is>
-          <t>Multicolored Spring Florals</t>
-        </is>
-      </c>
-      <c r="F166" s="8" t="inlineStr">
-        <is>
-          <t>This tumbler is bringing all the spring feels with its vibrant floral design, perfect for sipping your iced coffee, smoothies, or water in style. Whether you’re soaking up the sunshine at the park or just need a cute, practical accessory for your everyday life, this 38 oz tumbler has you covered. With a handy side handle and a fit that slides right</t>
-        </is>
-      </c>
-      <c r="G166" s="8" t="inlineStr"/>
-      <c r="H166" s="8" t="inlineStr"/>
-      <c r="I166" s="8" t="inlineStr"/>
-      <c r="J166" s="8" t="inlineStr"/>
-      <c r="K166" s="8" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="6" t="n">
-        <v>166</v>
-      </c>
-      <c r="B167" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C167" s="8" t="inlineStr">
-        <is>
-          <t>Subtle Strawberry 38 Oz Tumbler Cup</t>
-        </is>
-      </c>
-      <c r="D167" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E167" s="8" t="inlineStr">
-        <is>
-          <t>Pink Strawberry</t>
-        </is>
-      </c>
-      <c r="F167" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Here’s a tumbler that’s berry cute and ready to be your hydration sidekick all day! The Subtle Strawberry 38 Oz Tumbler brings a fresh, understated strawberry pattern for those who love a hint of sweetness with their style. This travel tumbler cup has a sturdy handle for easy carry, fits perfectly in any car cup holder (road trip, anyone?), and is </t>
-        </is>
-      </c>
-      <c r="G167" s="8" t="inlineStr"/>
-      <c r="H167" s="8" t="inlineStr"/>
-      <c r="I167" s="8" t="inlineStr"/>
-      <c r="J167" s="8" t="inlineStr"/>
-      <c r="K167" s="8" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="6" t="n">
-        <v>167</v>
-      </c>
-      <c r="B168" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C168" s="8" t="inlineStr">
-        <is>
-          <t>Sweet Orange Cup Tumbler</t>
-        </is>
-      </c>
-      <c r="D168" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E168" s="8" t="inlineStr">
-        <is>
-          <t>Light Pink</t>
-        </is>
-      </c>
-      <c r="F168" s="8" t="inlineStr">
-        <is>
-          <t>Fresh Orange Print Tumbler for Summer Days If summer had a signature cup, it would be the Sweet Orange Tumbler with Straw. Designed for the girl who loves bright colors, fun prints, and a little sunshine in her everyday routine, this tumbler brings citrus style to all your favorite moments. Whether you’re packing your beach bag, grabbing your morni</t>
-        </is>
-      </c>
-      <c r="G168" s="8" t="inlineStr"/>
-      <c r="H168" s="8" t="inlineStr"/>
-      <c r="I168" s="8" t="inlineStr"/>
-      <c r="J168" s="8" t="inlineStr"/>
-      <c r="K168" s="8" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="6" t="n">
-        <v>168</v>
-      </c>
-      <c r="B169" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C169" s="8" t="inlineStr">
-        <is>
-          <t>Tennis Social Club 38 Oz Tumbler with Lid Handle</t>
-        </is>
-      </c>
-      <c r="D169" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E169" s="8" t="inlineStr">
-        <is>
-          <t>Light Pink Tennis</t>
-        </is>
-      </c>
-      <c r="F169" s="8" t="inlineStr">
-        <is>
-          <t>Whether you're serving aces on the court or just need a cool way to stay hydrated, this Mimmolo Tennis Social Club tumbler is your perfect match! With a top lid handle and side handle, it’s super easy to grab and go, and the 38 oz size means you can sip on your favorite drink all day long. Plus, it fits perfectly in your cup holder, so you can keep</t>
-        </is>
-      </c>
-      <c r="G169" s="8" t="inlineStr"/>
-      <c r="H169" s="8" t="inlineStr"/>
-      <c r="I169" s="8" t="inlineStr"/>
-      <c r="J169" s="8" t="inlineStr"/>
-      <c r="K169" s="8" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="6" t="n">
-        <v>169</v>
-      </c>
-      <c r="B170" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C170" s="8" t="inlineStr">
-        <is>
-          <t>Tumbler Cup 38 Oz Jug (Yellow and Aqua Striped)</t>
-        </is>
-      </c>
-      <c r="D170" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E170" s="8" t="inlineStr">
-        <is>
-          <t>Yellow and Aqua</t>
-        </is>
-      </c>
-      <c r="F170" s="8" t="inlineStr">
-        <is>
-          <t>Cutest Travel Tumbler Cup with Built-In Straw + Dual Handles Ready to meet the tumbler of your dreams? Our yellow and aqua striped 38 oz tumbler cup is designed to make hydration not just easier but way more fun. With its vibrant two-toned stripes in a trendy yellow and blue and oversized capacity, this cute tumbler cup is ready for iced lattes, wa</t>
-        </is>
-      </c>
-      <c r="G170" s="8" t="inlineStr"/>
-      <c r="H170" s="8" t="inlineStr"/>
-      <c r="I170" s="8" t="inlineStr"/>
-      <c r="J170" s="8" t="inlineStr"/>
-      <c r="K170" s="8" t="inlineStr"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="6" t="n">
-        <v>170</v>
-      </c>
-      <c r="B171" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C171" s="8" t="inlineStr">
-        <is>
-          <t>Whimsical Roses Tumbler with Straw</t>
-        </is>
-      </c>
-      <c r="D171" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E171" s="8" t="inlineStr">
-        <is>
-          <t>Light Pink</t>
-        </is>
-      </c>
-      <c r="F171" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Your New Favorite Floral Tumbler with Straw The Whimsical Roses Tumbler Cup brings joyful, garden-inspired energy to every part of your day. Designed for anyone who loves florals, fun, and accessories that feel instantly uplifting, this tumbler with straw turns something as simple as staying hydrated into a bright, stylish moment. If you like your </t>
-        </is>
-      </c>
-      <c r="G171" s="8" t="inlineStr"/>
-      <c r="H171" s="8" t="inlineStr"/>
-      <c r="I171" s="8" t="inlineStr"/>
-      <c r="J171" s="8" t="inlineStr"/>
-      <c r="K171" s="8" t="inlineStr"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="6" t="n">
-        <v>171</v>
-      </c>
-      <c r="B172" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C172" s="8" t="inlineStr">
-        <is>
-          <t>XO Cherries Valentine's Day Tumbler with Lid Handle</t>
-        </is>
-      </c>
-      <c r="D172" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E172" s="8" t="inlineStr">
-        <is>
-          <t>Mint XO Cherries</t>
-        </is>
-      </c>
-      <c r="F172" s="8" t="inlineStr">
-        <is>
-          <t>Love You Cherry Much: Your Cutest Tumbler Yet Sippin' sweet never looked so cute! This XO Cherries Stainless Steel Tumbler is your go-to for flirty hydration. Covered in cherry and kiss motifs, it adds a playful touch to your daily coffee or matcha moment. With a sturdy lid and comfy handle, this tumbler cup is ready for everything from early morni</t>
-        </is>
-      </c>
-      <c r="G172" s="8" t="inlineStr"/>
-      <c r="H172" s="8" t="inlineStr"/>
-      <c r="I172" s="8" t="inlineStr"/>
-      <c r="J172" s="8" t="inlineStr"/>
-      <c r="K172" s="8" t="inlineStr"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="6" t="n">
-        <v>172</v>
-      </c>
-      <c r="B173" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C173" s="8" t="inlineStr">
-        <is>
-          <t>Yellow and Aqua Striped 30 Oz Tumbler Cup</t>
-        </is>
-      </c>
-      <c r="D173" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E173" s="8" t="inlineStr">
-        <is>
-          <t>Yellow and Aqua</t>
-        </is>
-      </c>
-      <c r="F173" s="8" t="inlineStr">
-        <is>
-          <t>Bold &amp; Bright Striped Tumbler Cup for Everyday Hydration Hydration, but make it cute. Our striped tumbler cup in yellow and aqua blue is the perfect mix of trendy design and practical function. With playful pastel stripes and a sturdy handle, this travel tumbler cup keeps your drinks cold for hours (or hot if that’s your vibe). Lightweight yet dura</t>
-        </is>
-      </c>
-      <c r="G173" s="8" t="inlineStr"/>
-      <c r="H173" s="8" t="inlineStr"/>
-      <c r="I173" s="8" t="inlineStr"/>
-      <c r="J173" s="8" t="inlineStr"/>
-      <c r="K173" s="8" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="6" t="n">
-        <v>173</v>
-      </c>
-      <c r="B174" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C174" s="8" t="inlineStr">
-        <is>
-          <t>Zesty Lemons Drink Tumbler</t>
-        </is>
-      </c>
-      <c r="D174" s="8" t="inlineStr">
-        <is>
-          <t>tumblers</t>
-        </is>
-      </c>
-      <c r="E174" s="8" t="inlineStr">
-        <is>
-          <t>Light Blue</t>
-        </is>
-      </c>
-      <c r="F174" s="8" t="inlineStr">
-        <is>
-          <t>Refresh Your Routine with the Zesty Lemons Tumbler If your drinkware could capture the feeling of a perfect summer afternoon, it would look exactly like the Zesty Lemons Tumbler Cup. This stainless steel reusable tumbler is made for the girl who loves warm weather, colorful accessories, and anything that brings a little joy to her daily routine. Wi</t>
-        </is>
-      </c>
-      <c r="G174" s="8" t="inlineStr"/>
-      <c r="H174" s="8" t="inlineStr"/>
-      <c r="I174" s="8" t="inlineStr"/>
-      <c r="J174" s="8" t="inlineStr"/>
-      <c r="K174" s="8" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="6" t="n">
-        <v>174</v>
-      </c>
-      <c r="B175" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C175" s="8" t="inlineStr">
-        <is>
-          <t>Black Puffer Water Bottle Carrier Bag</t>
-        </is>
-      </c>
-      <c r="D175" s="8" t="inlineStr">
-        <is>
-          <t>water bottle carrier</t>
-        </is>
-      </c>
-      <c r="E175" s="8" t="inlineStr">
-        <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="F175" s="8" t="inlineStr">
-        <is>
-          <t>11" x 6" 100% polyester snap closure exterior zipper pocket exterior phone pocket strap extends to 54.5" velcro strap to fit any bottle size</t>
-        </is>
-      </c>
-      <c r="G175" s="8" t="inlineStr"/>
-      <c r="H175" s="8" t="inlineStr"/>
-      <c r="I175" s="8" t="inlineStr"/>
-      <c r="J175" s="8" t="inlineStr"/>
-      <c r="K175" s="8" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="6" t="n">
-        <v>175</v>
-      </c>
-      <c r="B176" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C176" s="8" t="inlineStr">
-        <is>
-          <t>Hot Pink Two-Toned Water Bottle Holder</t>
-        </is>
-      </c>
-      <c r="D176" s="8" t="inlineStr">
-        <is>
-          <t>water bottle carrier</t>
-        </is>
-      </c>
-      <c r="E176" s="8" t="inlineStr">
-        <is>
-          <t>Hot Pink</t>
-        </is>
-      </c>
-      <c r="F176" s="8" t="inlineStr">
-        <is>
-          <t>Too Pretty to Spill: The Hot Pink Tumbler Carrier Bag Your tumbler deserves a cute bestie too! Introducing the Hot Pink Water Bottle Carrier Bag with Strap, the accessory that turns staying hydrated into a full-on fashion statement. Designed for the girl who’s always got a drink in hand (and a vibe to match), this tumbler carrier bag is the perfect</t>
-        </is>
-      </c>
-      <c r="G176" s="8" t="inlineStr"/>
-      <c r="H176" s="8" t="inlineStr"/>
-      <c r="I176" s="8" t="inlineStr"/>
-      <c r="J176" s="8" t="inlineStr"/>
-      <c r="K176" s="8" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="6" t="n">
-        <v>176</v>
-      </c>
-      <c r="B177" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C177" s="8" t="inlineStr">
-        <is>
-          <t>Light Blue Water Bottle Carrier Bag with Strap</t>
-        </is>
-      </c>
-      <c r="D177" s="8" t="inlineStr">
-        <is>
-          <t>water bottle carrier</t>
-        </is>
-      </c>
-      <c r="E177" s="8" t="inlineStr">
-        <is>
-          <t>Light Blue</t>
-        </is>
-      </c>
-      <c r="F177" s="8" t="inlineStr">
-        <is>
-          <t>Two-Toned, Hands-Free, and Totally Cute Your tumbler deserves an outfit too. The Light Blue Two-Toned Water Bottle Holder is here to make hydration so much cuter. Designed for the girl who loves matching her coffee cup to her outfit, this tumbler carrier bag combines convenience, comfort, and totally Pinterest-worthy style. With its soft quilted te</t>
-        </is>
-      </c>
-      <c r="G177" s="8" t="inlineStr"/>
-      <c r="H177" s="8" t="inlineStr"/>
-      <c r="I177" s="8" t="inlineStr"/>
-      <c r="J177" s="8" t="inlineStr"/>
-      <c r="K177" s="8" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="6" t="n">
-        <v>177</v>
-      </c>
-      <c r="B178" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C178" s="8" t="inlineStr">
-        <is>
-          <t>Mauve Quilted Tumbler Carrier Bag</t>
-        </is>
-      </c>
-      <c r="D178" s="8" t="inlineStr">
-        <is>
-          <t>water bottle carrier</t>
-        </is>
-      </c>
-      <c r="E178" s="8" t="inlineStr">
-        <is>
-          <t>Mauve</t>
-        </is>
-      </c>
-      <c r="F178" s="8" t="inlineStr">
-        <is>
-          <t>11” x 6” 100% polyester snap closure exterior zipper pocket exterior phone pocket strap extends to 54.5” velcro strap to fit any bottle size</t>
-        </is>
-      </c>
-      <c r="G178" s="8" t="inlineStr"/>
-      <c r="H178" s="8" t="inlineStr"/>
-      <c r="I178" s="8" t="inlineStr"/>
-      <c r="J178" s="8" t="inlineStr"/>
-      <c r="K178" s="8" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="6" t="n">
-        <v>178</v>
-      </c>
-      <c r="B179" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C179" s="8" t="inlineStr">
-        <is>
-          <t>Navy Two-Toned Quilted Water Bottle Purse</t>
-        </is>
-      </c>
-      <c r="D179" s="8" t="inlineStr">
-        <is>
-          <t>water bottle carrier</t>
-        </is>
-      </c>
-      <c r="E179" s="8" t="inlineStr">
-        <is>
-          <t>Navy</t>
-        </is>
-      </c>
-      <c r="F179" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Your Tumbler’s New BFF: The Quilted Crossbody Carrier Because your tumbler deserves a cute outfit too. Meet the Navy Two-Toned Tumbler Carrier Bag, the must-have accessory for tumblers everywhere. Designed to keep your favorite drink by your side (literally), this tumbler carrier bag is all about convenience, without sacrificing an ounce of style. </t>
-        </is>
-      </c>
-      <c r="G179" s="8" t="inlineStr"/>
-      <c r="H179" s="8" t="inlineStr"/>
-      <c r="I179" s="8" t="inlineStr"/>
-      <c r="J179" s="8" t="inlineStr"/>
-      <c r="K179" s="8" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="6" t="n">
-        <v>179</v>
-      </c>
-      <c r="B180" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C180" s="8" t="inlineStr">
-        <is>
-          <t>Sand Quilted Water Bottle Sling Bag</t>
-        </is>
-      </c>
-      <c r="D180" s="8" t="inlineStr">
-        <is>
-          <t>water bottle carrier</t>
-        </is>
-      </c>
-      <c r="E180" s="8" t="inlineStr">
-        <is>
-          <t>Sand</t>
-        </is>
-      </c>
-      <c r="F180" s="8" t="inlineStr">
-        <is>
-          <t>11‚Äù x 6‚Äù 100% polyester snap closure exterior zipper pocket exterior phone pocket strap extends to 54.5‚Äù velcro strap to fit any bottle size</t>
-        </is>
-      </c>
-      <c r="G180" s="8" t="inlineStr"/>
-      <c r="H180" s="8" t="inlineStr"/>
-      <c r="I180" s="8" t="inlineStr"/>
-      <c r="J180" s="8" t="inlineStr"/>
-      <c r="K180" s="8" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="6" t="n">
-        <v>180</v>
-      </c>
-      <c r="B181" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C181" s="8" t="inlineStr">
-        <is>
-          <t>Black &amp; Pink Mini Bows Wine Tumbler Cup</t>
-        </is>
-      </c>
-      <c r="D181" s="8" t="inlineStr">
-        <is>
-          <t>wine tumblers</t>
-        </is>
-      </c>
-      <c r="E181" s="8" t="inlineStr">
-        <is>
-          <t>Light Pink</t>
-        </is>
-      </c>
-      <c r="F181" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sip Cute With This Bow Moment If you love anything covered in bows, this Black &amp; Pink Mini Bows 12 Oz Wine Tumbler is about to be your new daily sidekick. The soft pink background and tiny black bows give it that sweet, girly vibe you can’t help but show off, and the stainless steel interior keeps every sip the perfect temperature. As an insulated </t>
-        </is>
-      </c>
-      <c r="G181" s="8" t="inlineStr"/>
-      <c r="H181" s="8" t="inlineStr"/>
-      <c r="I181" s="8" t="inlineStr"/>
-      <c r="J181" s="8" t="inlineStr"/>
-      <c r="K181" s="8" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="6" t="n">
-        <v>181</v>
-      </c>
-      <c r="B182" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C182" s="8" t="inlineStr">
-        <is>
-          <t>Cow Print Wine Tumbler Cup With Lid</t>
-        </is>
-      </c>
-      <c r="D182" s="8" t="inlineStr">
-        <is>
-          <t>wine tumblers</t>
-        </is>
-      </c>
-      <c r="E182" s="8" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
-      <c r="F182" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The Tumbler That Makes Every Sip More Fun Your drinkware lineup just got a whole lot cuter with this Cow Printed 12 Oz Wine Tumbler. If you love a fun western moment or just appreciate a bold print, this insulated wine tumbler is ready to go wherever you do. The stainless steel build keeps every sip cold longer, and the cow print turns an everyday </t>
-        </is>
-      </c>
-      <c r="G182" s="8" t="inlineStr"/>
-      <c r="H182" s="8" t="inlineStr"/>
-      <c r="I182" s="8" t="inlineStr"/>
-      <c r="J182" s="8" t="inlineStr"/>
-      <c r="K182" s="8" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="6" t="n">
-        <v>182</v>
-      </c>
-      <c r="B183" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C183" s="8" t="inlineStr">
-        <is>
-          <t>Dainty Florals Pink WINE TUMBLER Cup</t>
-        </is>
-      </c>
-      <c r="D183" s="8" t="inlineStr">
-        <is>
-          <t>wine tumblers</t>
-        </is>
-      </c>
-      <c r="E183" s="8" t="inlineStr">
-        <is>
-          <t>Light Pink and Blue Flowers</t>
-        </is>
-      </c>
-      <c r="F183" s="8" t="inlineStr">
-        <is>
-          <t>The Dainty Florals Pink Wine Tumbler is here to bring major soft girl vibes to your drink game. Featuring a delicate floral print on a pastel pink backdrop, this stemless tumbler is perfect for sipping in style—whether it's wine o'clock or matcha time. Double-wall insulation : Keeps drinks cold for hours or your coffee hot Portable &amp; chic : Perfect</t>
-        </is>
-      </c>
-      <c r="G183" s="8" t="inlineStr"/>
-      <c r="H183" s="8" t="inlineStr"/>
-      <c r="I183" s="8" t="inlineStr"/>
-      <c r="J183" s="8" t="inlineStr"/>
-      <c r="K183" s="8" t="inlineStr"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="6" t="n">
-        <v>183</v>
-      </c>
-      <c r="B184" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C184" s="8" t="inlineStr">
-        <is>
-          <t>Lucky Girl Western Insulated Wine Tumbler</t>
-        </is>
-      </c>
-      <c r="D184" s="8" t="inlineStr">
-        <is>
-          <t>wine tumblers</t>
-        </is>
-      </c>
-      <c r="E184" s="8" t="inlineStr">
-        <is>
-          <t>Lucky Mint</t>
-        </is>
-      </c>
-      <c r="F184" s="8" t="inlineStr">
-        <is>
-          <t>Sippin' in style just got a wild upgrade with the Lucky Girl Western Insulated Wine Tumbler ! This stemless tumbler is serving major western vibes with its fun, on-trend doodles and a poppin' design that’s cute and cowgirl chic . Whether you're sipping wine, iced tea, or a spicy margarita, this stemless wine tumbler keeps your drinks at the perfect</t>
-        </is>
-      </c>
-      <c r="G184" s="8" t="inlineStr"/>
-      <c r="H184" s="8" t="inlineStr"/>
-      <c r="I184" s="8" t="inlineStr"/>
-      <c r="J184" s="8" t="inlineStr"/>
-      <c r="K184" s="8" t="inlineStr"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="6" t="n">
-        <v>184</v>
-      </c>
-      <c r="B185" s="7" t="inlineStr">
-        <is>
-          <t>PENDING QUOTATION</t>
-        </is>
-      </c>
-      <c r="C185" s="8" t="inlineStr">
-        <is>
-          <t>Toile Coquette Bows WINE TUMBLER Cup</t>
-        </is>
-      </c>
-      <c r="D185" s="8" t="inlineStr">
-        <is>
-          <t>wine tumblers</t>
-        </is>
-      </c>
-      <c r="E185" s="8" t="inlineStr">
-        <is>
-          <t>Light Blue Bows</t>
-        </is>
-      </c>
-      <c r="F185" s="8" t="inlineStr">
-        <is>
-          <t>Sip in style with the Chinoiserie Coquette Bows Wine Tumbler ! This stemless tumbler is serving elegant meets flirty vibes with its chic toile-inspired print and dainty bow accents. Whether you’re toasting with your favorite wine, keeping your coffee hot, or indulging in a cozy tea moment, this tumbler has your back (and your drink). Double-wall in</t>
-        </is>
-      </c>
-      <c r="G185" s="8" t="inlineStr"/>
-      <c r="H185" s="8" t="inlineStr"/>
-      <c r="I185" s="8" t="inlineStr"/>
-      <c r="J185" s="8" t="inlineStr"/>
-      <c r="K185" s="8" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
